--- a/PIMMS Validation work/Skyline comparison data/Skyline_all_analyte_detection_frequency.xlsx
+++ b/PIMMS Validation work/Skyline comparison data/Skyline_all_analyte_detection_frequency.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\PFAS-IMplementor-for-Mass-Spectrometry--PIMMS-\PIMMS Validation work\Skyline comparison data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE3F2DEC-5B52-4DAF-8B77-42EFA13A296A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0C796A-5DA8-4F52-A5BF-2FFA8A8F0C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{79560FBE-CED3-4771-A659-93F59127F910}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79560FBE-CED3-4771-A659-93F59127F910}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="41" r:id="rId1"/>
@@ -26,32 +26,31 @@
     <sheet name="PFOS - Linear Native" sheetId="10" r:id="rId11"/>
     <sheet name="PFOS - Branched Native" sheetId="11" r:id="rId12"/>
     <sheet name="PFOS - Heavy" sheetId="12" r:id="rId13"/>
-    <sheet name="PFNS - Linear Native" sheetId="13" r:id="rId14"/>
-    <sheet name="PFDS - Linear Native" sheetId="14" r:id="rId15"/>
-    <sheet name="PFHxA - Heavy" sheetId="15" r:id="rId16"/>
-    <sheet name="PFHpA - Native" sheetId="16" r:id="rId17"/>
-    <sheet name="PFHpA - Heavy" sheetId="17" r:id="rId18"/>
-    <sheet name="PFOA - Branched Native" sheetId="18" r:id="rId19"/>
-    <sheet name="PFOA - Linear Native" sheetId="19" r:id="rId20"/>
-    <sheet name="PFOA - Linear Heavy" sheetId="20" r:id="rId21"/>
-    <sheet name="PFNA - Linear Native" sheetId="21" r:id="rId22"/>
-    <sheet name="PFNA - Heavy" sheetId="22" r:id="rId23"/>
-    <sheet name="PFDA - Linear Native" sheetId="23" r:id="rId24"/>
-    <sheet name="PFDA - Heavy" sheetId="24" r:id="rId25"/>
-    <sheet name="PFUdA - Heavy" sheetId="25" r:id="rId26"/>
-    <sheet name="PFDoA - Heavy" sheetId="26" r:id="rId27"/>
-    <sheet name="PFTeDA - Heavy" sheetId="27" r:id="rId28"/>
-    <sheet name="42 FTS - Heavy" sheetId="28" r:id="rId29"/>
-    <sheet name="62 FTS - Heavy" sheetId="29" r:id="rId30"/>
-    <sheet name="82 FTS - Heavy" sheetId="30" r:id="rId31"/>
-    <sheet name="FOSA - Heavy" sheetId="31" r:id="rId32"/>
-    <sheet name="NMeFOSAA - Heavy" sheetId="33" r:id="rId33"/>
-    <sheet name="NEtFOSAA - Heavy" sheetId="34" r:id="rId34"/>
-    <sheet name="NMeFOSA - Heavy " sheetId="35" r:id="rId35"/>
-    <sheet name="NMeFOSA - Heavy smaller peak" sheetId="36" r:id="rId36"/>
-    <sheet name="NEtFOSA - Heavy" sheetId="37" r:id="rId37"/>
-    <sheet name="NEtFOSA - Heavy smaller peak" sheetId="38" r:id="rId38"/>
-    <sheet name="HFPO-DA Heavy" sheetId="40" r:id="rId39"/>
+    <sheet name="PFDS - Linear Native" sheetId="14" r:id="rId14"/>
+    <sheet name="PFHxA - Heavy" sheetId="15" r:id="rId15"/>
+    <sheet name="PFHpA - Native" sheetId="16" r:id="rId16"/>
+    <sheet name="PFHpA - Heavy" sheetId="17" r:id="rId17"/>
+    <sheet name="PFOA - Branched Native" sheetId="18" r:id="rId18"/>
+    <sheet name="PFOA - Linear Native" sheetId="19" r:id="rId19"/>
+    <sheet name="PFOA - Linear Heavy" sheetId="20" r:id="rId20"/>
+    <sheet name="PFNA - Linear Native" sheetId="21" r:id="rId21"/>
+    <sheet name="PFNA - Heavy" sheetId="22" r:id="rId22"/>
+    <sheet name="PFDA - Linear Native" sheetId="23" r:id="rId23"/>
+    <sheet name="PFDA - Heavy" sheetId="24" r:id="rId24"/>
+    <sheet name="PFUdA - Heavy" sheetId="25" r:id="rId25"/>
+    <sheet name="PFDoA - Heavy" sheetId="26" r:id="rId26"/>
+    <sheet name="PFTeDA - Heavy" sheetId="27" r:id="rId27"/>
+    <sheet name="42 FTS - Heavy" sheetId="28" r:id="rId28"/>
+    <sheet name="62 FTS - Heavy" sheetId="29" r:id="rId29"/>
+    <sheet name="82 FTS - Heavy" sheetId="30" r:id="rId30"/>
+    <sheet name="FOSA - Heavy" sheetId="31" r:id="rId31"/>
+    <sheet name="NMeFOSAA - Heavy" sheetId="33" r:id="rId32"/>
+    <sheet name="NEtFOSAA - Heavy" sheetId="34" r:id="rId33"/>
+    <sheet name="NMeFOSA - Heavy " sheetId="35" r:id="rId34"/>
+    <sheet name="NMeFOSA - Heavy smaller peak" sheetId="36" r:id="rId35"/>
+    <sheet name="NEtFOSA - Heavy" sheetId="37" r:id="rId36"/>
+    <sheet name="NEtFOSA - Heavy smaller peak" sheetId="38" r:id="rId37"/>
+    <sheet name="HFPO-DA Heavy" sheetId="40" r:id="rId38"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -74,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="57">
   <si>
     <t>Method Blank 1</t>
   </si>
@@ -242,6 +241,9 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>Skyline average intensity</t>
   </si>
 </sst>
 </file>
@@ -623,16 +625,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06055A1B-F8E7-48F6-9BA6-ACEC0EB67378}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="54.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>55</v>
       </c>
@@ -645,8 +648,11 @@
       <c r="D1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -659,8 +665,11 @@
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>1529309.5961538462</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -670,8 +679,11 @@
       <c r="D3">
         <v>75</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>812.99585430438697</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -684,8 +696,11 @@
       <c r="D4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>7025.7919170673076</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -698,8 +713,11 @@
       <c r="D5">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>595234.8125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -712,8 +730,11 @@
       <c r="D6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>68730.022235576922</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -726,8 +747,11 @@
       <c r="D7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>2446575.451923077</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -738,8 +762,11 @@
       <c r="D8">
         <v>87.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>3572.077204777645</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -752,8 +779,11 @@
       <c r="D9">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>47056.896033653844</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -766,8 +796,11 @@
       <c r="D10">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>1592.8783240685102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -780,8 +813,11 @@
       <c r="D11">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>1659735.9840646891</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -794,8 +830,11 @@
       <c r="D12">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>1129186.9615384615</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -808,8 +847,11 @@
       <c r="D13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>2099178.355769231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -819,8 +861,11 @@
       <c r="D14">
         <v>37.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>949.35640775240381</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -833,8 +878,11 @@
       <c r="D15">
         <v>62.5</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>82487.594951923078</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -844,8 +892,11 @@
       <c r="D16">
         <v>87.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>3037.6404747596152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -858,8 +909,11 @@
       <c r="D17">
         <v>37.5</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>376820.66105769231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -872,8 +926,11 @@
       <c r="D18">
         <v>87.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>2563.6629920372602</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -886,8 +943,11 @@
       <c r="D19">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>193456.36618276744</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -900,8 +960,11 @@
       <c r="D20">
         <v>37.5</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>679784.53365384613</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -911,8 +974,11 @@
       <c r="D21">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>29166.224696232723</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -925,8 +991,11 @@
       <c r="D22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>322662.32331730769</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -936,8 +1005,11 @@
       <c r="D23">
         <v>62.5</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>2809.4590594951924</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -950,8 +1022,11 @@
       <c r="D24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24">
+        <v>225773.68629807694</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -964,8 +1039,11 @@
       <c r="D25">
         <v>87.5</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25">
+        <v>150811.41887019231</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>44</v>
       </c>
@@ -978,8 +1056,11 @@
       <c r="D26">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26">
+        <v>83036.461219200719</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>45</v>
       </c>
@@ -992,8 +1073,11 @@
       <c r="D27">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27">
+        <v>56380.275240384617</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -1006,8 +1090,11 @@
       <c r="D28">
         <v>62.5</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28">
+        <v>334305.99278846156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>47</v>
       </c>
@@ -1020,8 +1107,11 @@
       <c r="D29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29">
+        <v>401397.44951923075</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>48</v>
       </c>
@@ -1034,8 +1124,11 @@
       <c r="D30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30">
+        <v>378996.14423076925</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -1048,8 +1141,11 @@
       <c r="D31">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31">
+        <v>329612.18509615387</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>50</v>
       </c>
@@ -1062,8 +1158,11 @@
       <c r="D32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32">
+        <v>168178.23497596153</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>51</v>
       </c>
@@ -1076,8 +1175,11 @@
       <c r="D33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33">
+        <v>122014.38551682692</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>52</v>
       </c>
@@ -1090,8 +1192,11 @@
       <c r="D34">
         <v>100</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34">
+        <v>100535.16286057692</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -1104,8 +1209,11 @@
       <c r="D35">
         <v>25</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35">
+        <v>3821.6311035156255</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -1118,8 +1226,11 @@
       <c r="D36">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36">
+        <v>64792.799278846156</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>53</v>
       </c>
@@ -1132,8 +1243,11 @@
       <c r="D37">
         <v>100</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37">
+        <v>7437.6379582331729</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>54</v>
       </c>
@@ -1145,6 +1259,9 @@
       </c>
       <c r="D38">
         <v>75</v>
+      </c>
+      <c r="E38">
+        <v>1827.4127385066115</v>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3582B0E6-5A5B-4C02-98A3-54931C7DC318}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1399,6 +1516,12 @@
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>1592.8783240685102</v>
       </c>
     </row>
   </sheetData>
@@ -1408,7 +1531,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FC1C3A-F78D-440D-BD66-AE87DD7194BA}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1653,6 +1776,12 @@
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>1659735.9840646891</v>
       </c>
     </row>
   </sheetData>
@@ -1662,7 +1791,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B920CE9E-75B8-4A59-A12E-E0D1E93B39D0}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1907,6 +2036,12 @@
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>1129186.9615384615</v>
       </c>
     </row>
   </sheetData>
@@ -1916,7 +2051,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8555E29D-7B73-40B6-8CCA-CFFCF19C489C}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2161,6 +2296,12 @@
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>2099178.355769231</v>
       </c>
     </row>
   </sheetData>
@@ -2169,8 +2310,8 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87A9F267-6390-4D31-B81E-773ED36C299B}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F76DF-C21E-4C19-B3CD-AB910E26AFC2}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2252,19 +2393,19 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>4387.17626953125</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>0</v>
+        <v>4387.17626953125</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2272,19 +2413,19 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>5261.6826171875</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>0</v>
+        <v>5261.6826171875</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2292,11 +2433,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>70.671791076660199</v>
+        <v>2692.7744140625</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>70.671791076660199</v>
+        <v>2692.7744140625</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -2410,11 +2551,17 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>7.6923076923076925</v>
+        <v>23.076923076923077</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>12.5</v>
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>949.35640775240381</v>
       </c>
     </row>
   </sheetData>
@@ -2423,8 +2570,8 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F76DF-C21E-4C19-B3CD-AB910E26AFC2}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBA0397-8353-463A-882C-3FE22A5D5D75}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2446,11 +2593,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>69798.1015625</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2458,11 +2605,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>68369.4453125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2470,11 +2617,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>66003.2578125</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2482,11 +2629,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>81546.578125</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2494,11 +2641,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>65632.34375</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2506,11 +2653,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>4387.17626953125</v>
+        <v>92055.8828125</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>4387.17626953125</v>
+        <v>2187.5919477746793</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -2526,11 +2673,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>5261.6826171875</v>
+        <v>105429.296875</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>5261.6826171875</v>
+        <v>15561.006010274679</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -2546,11 +2693,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2692.7744140625</v>
+        <v>99373.421875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>2692.7744140625</v>
+        <v>9505.1310102746793</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -2566,15 +2713,15 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>84551.8671875</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-5316.4236772253207</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
@@ -2586,19 +2733,19 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>92856.8046875</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2988.5138227746793</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2606,19 +2753,19 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>92011.265625</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2142.9747602746793</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2626,15 +2773,15 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>79530.109375</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-10338.181489725321</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
@@ -2646,15 +2793,15 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>75180.359375</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-14687.931489725321</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
@@ -2664,11 +2811,17 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>23.076923076923077</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>37.5</v>
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>82487.594951923078</v>
       </c>
     </row>
   </sheetData>
@@ -2677,8 +2830,8 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBA0397-8353-463A-882C-3FE22A5D5D75}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C066AFD-AB72-49D4-8676-B34BA24294E8}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2700,11 +2853,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>69798.1015625</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2712,11 +2865,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>68369.4453125</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2724,11 +2877,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>66003.2578125</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2736,11 +2889,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>81546.578125</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2748,11 +2901,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>65632.34375</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2760,11 +2913,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>92055.8828125</v>
+        <v>6431.6748046875</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>2187.5919477746793</v>
+        <v>6431.6748046875</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -2780,11 +2933,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>105429.296875</v>
+        <v>9010.33984375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>15561.006010274679</v>
+        <v>9010.33984375</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -2800,11 +2953,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>99373.421875</v>
+        <v>8583.357421875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>9505.1310102746793</v>
+        <v>8583.357421875</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -2820,11 +2973,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>84551.8671875</v>
+        <v>3210.9296875</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-5316.4236772253207</v>
+        <v>3210.9296875</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -2832,7 +2985,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2840,11 +2993,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>92856.8046875</v>
+        <v>4768.36865234375</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>2988.5138227746793</v>
+        <v>4768.36865234375</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -2860,11 +3013,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>92011.265625</v>
+        <v>5185.181640625</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>2142.9747602746793</v>
+        <v>5185.181640625</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -2880,11 +3033,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>79530.109375</v>
+        <v>2299.47412109375</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-10338.181489725321</v>
+        <v>2299.47412109375</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -2892,7 +3045,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2900,15 +3053,15 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>75180.359375</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-14687.931489725321</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
@@ -2918,11 +3071,17 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>100</v>
+        <v>53.846153846153847</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>62.5</v>
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>3037.6404747596152</v>
       </c>
     </row>
   </sheetData>
@@ -2931,8 +3090,8 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C066AFD-AB72-49D4-8676-B34BA24294E8}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75A288D7-A45C-4CB7-B512-97C064450FDC}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2954,11 +3113,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>328549.25</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2966,11 +3125,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>349568.15625</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2978,11 +3137,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>344527.125</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2990,11 +3149,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>372575.28125</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -3002,11 +3161,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>346503.15625</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -3014,11 +3173,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>6431.6748046875</v>
+        <v>382461.84375</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>6431.6748046875</v>
+        <v>-13279.971021820558</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -3026,7 +3185,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -3034,11 +3193,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>9010.33984375</v>
+        <v>425844.875</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>9010.33984375</v>
+        <v>30103.060228179442</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -3054,11 +3213,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>8583.357421875</v>
+        <v>416779.125</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>8583.357421875</v>
+        <v>21037.310228179442</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -3074,11 +3233,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>3210.9296875</v>
+        <v>380325.96875</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>3210.9296875</v>
+        <v>-15415.846021820558</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -3086,7 +3245,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -3094,11 +3253,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>4768.36865234375</v>
+        <v>382843.09375</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>4768.36865234375</v>
+        <v>-12898.721021820558</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -3106,7 +3265,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3114,11 +3273,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>5185.181640625</v>
+        <v>415339.1875</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>5185.181640625</v>
+        <v>19597.372728179442</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -3134,11 +3293,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>2299.47412109375</v>
+        <v>373603.625</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>2299.47412109375</v>
+        <v>-22138.189771820558</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -3146,7 +3305,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -3154,15 +3313,15 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>379747.90625</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-15993.908521820558</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
@@ -3172,11 +3331,17 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>53.846153846153847</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>87.5</v>
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>376820.66105769231</v>
       </c>
     </row>
   </sheetData>
@@ -3185,8 +3350,8 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75A288D7-A45C-4CB7-B512-97C064450FDC}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D17BA435-9AAF-482D-99AF-F69269029229}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3208,11 +3373,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>328549.25</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3220,11 +3385,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>349568.15625</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -3232,11 +3397,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>344527.125</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -3244,11 +3409,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>372575.28125</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -3256,11 +3421,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>346503.15625</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -3268,11 +3433,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>382461.84375</v>
+        <v>4098.52978515625</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-13279.971021820558</v>
+        <v>4098.52978515625</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -3280,7 +3445,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -3288,11 +3453,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>425844.875</v>
+        <v>4639.470703125</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>30103.060228179442</v>
+        <v>4639.470703125</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -3308,11 +3473,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>416779.125</v>
+        <v>2400.79418945313</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>21037.310228179442</v>
+        <v>2400.79418945313</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -3328,11 +3493,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>380325.96875</v>
+        <v>7682.24951171875</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-15415.846021820558</v>
+        <v>7682.24951171875</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -3340,7 +3505,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -3348,11 +3513,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>382843.09375</v>
+        <v>5800.00830078125</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-12898.721021820558</v>
+        <v>5800.00830078125</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -3360,7 +3525,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3368,11 +3533,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>415339.1875</v>
+        <v>6797.3125</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>19597.372728179442</v>
+        <v>6797.3125</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -3388,15 +3553,15 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>373603.625</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-22138.189771820558</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
@@ -3408,11 +3573,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>379747.90625</v>
+        <v>1909.25390625</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-15993.908521820558</v>
+        <v>1909.25390625</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -3420,17 +3585,23 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>100</v>
+        <v>53.846153846153847</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>37.5</v>
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>2563.6629920372602</v>
       </c>
     </row>
   </sheetData>
@@ -3439,8 +3610,8 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D17BA435-9AAF-482D-99AF-F69269029229}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B373B079-11F4-48D2-A74B-22D8B71CC3A8}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3462,11 +3633,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>4526.8828125</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3474,11 +3645,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1683.16320800781</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -3486,11 +3657,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>3053.68090820313</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -3498,11 +3669,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>4303.89892578125</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -3510,11 +3681,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1694.91577148438</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -3522,11 +3693,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>4098.52978515625</v>
+        <v>293705.9375</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>4098.52978515625</v>
+        <v>286557.0493163896</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -3542,11 +3713,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>4639.470703125</v>
+        <v>300910.03125</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>4639.470703125</v>
+        <v>293761.1430663896</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -3562,11 +3733,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2400.79418945313</v>
+        <v>286102.0625</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>2400.79418945313</v>
+        <v>278953.1743163896</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -3582,11 +3753,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>7682.24951171875</v>
+        <v>355375.53125</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>7682.24951171875</v>
+        <v>348226.6430663896</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -3602,11 +3773,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>5800.00830078125</v>
+        <v>387440.125</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>5800.00830078125</v>
+        <v>380291.2368163896</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -3622,11 +3793,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>6797.3125</v>
+        <v>374613.03125</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>6797.3125</v>
+        <v>367464.1430663896</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -3642,19 +3813,19 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>264580.75</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>257431.86181638957</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -3662,11 +3833,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>1909.25390625</v>
+        <v>236942.75</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>1909.25390625</v>
+        <v>229793.86181638957</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -3680,11 +3851,17 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>53.846153846153847</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>87.5</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>193456.36618276744</v>
       </c>
     </row>
   </sheetData>
@@ -3694,7 +3871,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64FBD9A9-81EB-4FCF-9AE1-F11107D115C5}">
-  <dimension ref="G1:K16"/>
+  <dimension ref="G1:K17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -3947,14 +4124,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H17">
+        <f>AVERAGE(H2:H14)</f>
+        <v>1529309.5961538462</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B373B079-11F4-48D2-A74B-22D8B71CC3A8}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D90E46-680E-43C5-899C-332D591CDF68}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3976,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>4526.8828125</v>
+        <v>626116.5</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
@@ -3988,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>1683.16320800781</v>
+        <v>659753</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
@@ -4000,7 +4183,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3053.68090820313</v>
+        <v>661851.5</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -4012,7 +4195,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>4303.89892578125</v>
+        <v>685317.75</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
@@ -4024,7 +4207,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1694.91577148438</v>
+        <v>653382.125</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -4036,11 +4219,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>293705.9375</v>
+        <v>608325.9375</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>286557.0493163896</v>
+        <v>-112588.77570361143</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -4048,7 +4231,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -4056,11 +4239,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>300910.03125</v>
+        <v>641939.3125</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>293761.1430663896</v>
+        <v>-78975.400703611434</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -4068,7 +4251,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -4076,11 +4259,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>286102.0625</v>
+        <v>620447.0625</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>278953.1743163896</v>
+        <v>-100467.65070361143</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -4088,7 +4271,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4096,11 +4279,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>355375.53125</v>
+        <v>753973.4375</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>348226.6430663896</v>
+        <v>33058.724296388566</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -4116,11 +4299,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>387440.125</v>
+        <v>754605.6875</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>380291.2368163896</v>
+        <v>33690.974296388566</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -4136,11 +4319,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>374613.03125</v>
+        <v>797468.3125</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>367464.1430663896</v>
+        <v>76553.599296388566</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -4156,11 +4339,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>264580.75</v>
+        <v>679001</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>257431.86181638957</v>
+        <v>-41913.713203611434</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -4168,7 +4351,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -4176,11 +4359,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>236942.75</v>
+        <v>695017.3125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>229793.86181638957</v>
+        <v>-25897.400703611434</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -4188,7 +4371,7 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -4198,7 +4381,13 @@
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>100</v>
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>679784.53365384613</v>
       </c>
     </row>
   </sheetData>
@@ -4207,8 +4396,8 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D90E46-680E-43C5-899C-332D591CDF68}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8B39702-5FBC-47D5-A77D-76A613184E77}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4230,11 +4419,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>626116.5</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4242,11 +4431,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>659753</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4254,11 +4443,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>661851.5</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4266,11 +4455,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>685317.75</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4278,7 +4467,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>653382.125</v>
+        <v>59.975738525390597</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -4290,11 +4479,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>608325.9375</v>
+        <v>38310.765625</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-112588.77570361143</v>
+        <v>38218.304580288808</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -4302,7 +4491,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -4310,11 +4499,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>641939.3125</v>
+        <v>39549.5234375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-78975.400703611434</v>
+        <v>39457.062392788808</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -4322,7 +4511,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -4330,11 +4519,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>620447.0625</v>
+        <v>37016.54296875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-100467.65070361143</v>
+        <v>36924.081924038808</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -4342,7 +4531,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4350,11 +4539,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>753973.4375</v>
+        <v>66430.625</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>33058.724296388566</v>
+        <v>66338.163955288808</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -4370,11 +4559,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>754605.6875</v>
+        <v>57609.11328125</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>33690.974296388566</v>
+        <v>57516.652236538808</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -4390,11 +4579,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>797468.3125</v>
+        <v>64442.453125</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>76553.599296388566</v>
+        <v>64349.992080288808</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -4410,11 +4599,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>679001</v>
+        <v>38793.4296875</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-41913.713203611434</v>
+        <v>38700.968642788808</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -4422,7 +4611,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -4430,11 +4619,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>695017.3125</v>
+        <v>36948.4921875</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-25897.400703611434</v>
+        <v>36856.031142788808</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -4442,17 +4631,23 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>100</v>
+        <v>69.230769230769226</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>37.5</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>29166.224696232723</v>
       </c>
     </row>
   </sheetData>
@@ -4461,8 +4656,8 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8B39702-5FBC-47D5-A77D-76A613184E77}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3842B4B-8929-4ECB-8BD3-19501EE1AC1C}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4484,11 +4679,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>326238.34375</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4496,11 +4691,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>354287.03125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4508,11 +4703,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>343340.6875</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4520,11 +4715,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>358255.15625</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4532,7 +4727,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>59.975738525390597</v>
+        <v>344247.875</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -4544,11 +4739,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>38310.765625</v>
+        <v>268956.375</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>38218.304580288808</v>
+        <v>-113573.40936318471</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -4556,7 +4751,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -4564,11 +4759,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>39549.5234375</v>
+        <v>266823.15625</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>39457.062392788808</v>
+        <v>-115706.62811318471</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -4576,7 +4771,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -4584,11 +4779,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>37016.54296875</v>
+        <v>243906.234375</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>36924.081924038808</v>
+        <v>-138623.54998818471</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -4596,7 +4791,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4604,11 +4799,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>66430.625</v>
+        <v>354071.0625</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>66338.163955288808</v>
+        <v>-28458.721863184706</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -4616,7 +4811,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -4624,11 +4819,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>57609.11328125</v>
+        <v>363293.71875</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>57516.652236538808</v>
+        <v>-19236.065613184706</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -4636,7 +4831,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -4644,11 +4839,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>64442.453125</v>
+        <v>367311.15625</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>64349.992080288808</v>
+        <v>-15218.628113184706</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -4656,7 +4851,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -4664,11 +4859,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>38793.4296875</v>
+        <v>298605.25</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>38700.968642788808</v>
+        <v>-83924.534363184706</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -4676,7 +4871,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -4684,11 +4879,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>36948.4921875</v>
+        <v>305274.15625</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>36856.031142788808</v>
+        <v>-77255.628113184706</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -4696,17 +4891,23 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>69.230769230769226</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>100</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>322662.32331730769</v>
       </c>
     </row>
   </sheetData>
@@ -4715,8 +4916,8 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3842B4B-8929-4ECB-8BD3-19501EE1AC1C}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10A91543-3248-43B1-8CC1-89E16ADD1168}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4738,11 +4939,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>326238.34375</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4750,11 +4951,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>354287.03125</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4762,11 +4963,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>343340.6875</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4774,11 +4975,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>358255.15625</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4786,11 +4987,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>344247.875</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4798,11 +4999,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>268956.375</v>
+        <v>5807.3310546875</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-113573.40936318471</v>
+        <v>5807.3310546875</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -4810,7 +5011,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -4818,11 +5019,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>266823.15625</v>
+        <v>4705.115234375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-115706.62811318471</v>
+        <v>4705.115234375</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -4830,7 +5031,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -4838,11 +5039,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>243906.234375</v>
+        <v>7633.1455078125</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-138623.54998818471</v>
+        <v>7633.1455078125</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -4850,7 +5051,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4858,11 +5059,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>354071.0625</v>
+        <v>9279.103515625</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-28458.721863184706</v>
+        <v>9279.103515625</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -4870,7 +5071,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -4878,15 +5079,15 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>363293.71875</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-19236.065613184706</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
@@ -4898,11 +5099,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>367311.15625</v>
+        <v>9098.2724609375</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-15218.628113184706</v>
+        <v>9098.2724609375</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -4910,7 +5111,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -4918,15 +5119,15 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>298605.25</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-83924.534363184706</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
@@ -4938,15 +5139,15 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>305274.15625</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-77255.628113184706</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
@@ -4956,11 +5157,17 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>100</v>
+        <v>38.461538461538467</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>0</v>
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>2809.4590594951924</v>
       </c>
     </row>
   </sheetData>
@@ -4969,8 +5176,8 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10A91543-3248-43B1-8CC1-89E16ADD1168}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F62F1E8F-7775-41F2-A9E3-56941E817487}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4992,11 +5199,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>245209.03125</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5004,11 +5211,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>240123.96875</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5016,11 +5223,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>264158.40625</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5028,11 +5235,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>276169.4375</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5040,11 +5247,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>243046.46875</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5052,11 +5259,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>5807.3310546875</v>
+        <v>204720.671875</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>5807.3310546875</v>
+        <v>-96077.495010878542</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -5064,7 +5271,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5072,11 +5279,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>4705.115234375</v>
+        <v>208431.9375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>4705.115234375</v>
+        <v>-92366.229385878542</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -5084,7 +5291,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5092,11 +5299,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>7633.1455078125</v>
+        <v>196465.875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>7633.1455078125</v>
+        <v>-104332.29188587854</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -5104,7 +5311,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5112,11 +5319,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>9279.103515625</v>
+        <v>280239.84375</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>9279.103515625</v>
+        <v>-20558.323135878542</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -5124,7 +5331,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5132,15 +5339,15 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>279034.875</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-21763.291885878542</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
@@ -5152,11 +5359,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>9098.2724609375</v>
+        <v>272495.46875</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>9098.2724609375</v>
+        <v>-28302.698135878542</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -5164,7 +5371,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5172,15 +5379,15 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>224961.9375</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-75836.229385878542</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
@@ -5196,7 +5403,7 @@
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-300798.16688587854</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -5210,11 +5417,17 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>38.461538461538467</v>
+        <v>92.307692307692307</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>62.5</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>225773.68629807694</v>
       </c>
     </row>
   </sheetData>
@@ -5223,8 +5436,8 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F62F1E8F-7775-41F2-A9E3-56941E817487}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A757A9C-A327-434D-82A9-1F401F37251F}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5246,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>245209.03125</v>
+        <v>117939.7109375</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
@@ -5258,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>240123.96875</v>
+        <v>90538.5078125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
@@ -5270,7 +5483,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>264158.40625</v>
+        <v>119213.4921875</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -5282,7 +5495,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>276169.4375</v>
+        <v>102652.8359375</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
@@ -5294,7 +5507,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>243046.46875</v>
+        <v>76029.9609375</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -5306,11 +5519,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>204720.671875</v>
+        <v>165324.015625</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-96077.495010878542</v>
+        <v>8854.3156763353618</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -5318,7 +5531,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5326,11 +5539,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>208431.9375</v>
+        <v>189902.265625</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-92366.229385878542</v>
+        <v>33432.565676335362</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -5338,7 +5551,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5346,11 +5559,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>196465.875</v>
+        <v>174142.65625</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-104332.29188587854</v>
+        <v>17672.956301335362</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -5358,7 +5571,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5366,11 +5579,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>280239.84375</v>
+        <v>200697.03125</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-20558.323135878542</v>
+        <v>44227.331301335362</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -5378,7 +5591,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5386,11 +5599,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>279034.875</v>
+        <v>196633.375</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-21763.291885878542</v>
+        <v>40163.675051335362</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -5398,7 +5611,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5406,11 +5619,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>272495.46875</v>
+        <v>205772.234375</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-28302.698135878542</v>
+        <v>49302.534426335362</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -5418,7 +5631,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5426,11 +5639,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>224961.9375</v>
+        <v>155182.109375</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-75836.229385878542</v>
+        <v>-1287.5905736646382</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -5446,29 +5659,35 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>166520.25</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-300798.16688587854</v>
+        <v>10050.550051335362</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>92.307692307692307</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>150811.41887019231</v>
       </c>
     </row>
   </sheetData>
@@ -5477,8 +5696,8 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A757A9C-A327-434D-82A9-1F401F37251F}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C61A7656-548B-4995-87CD-0D0D8FF30CE7}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5500,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>117939.7109375</v>
+        <v>17152.169921875</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
@@ -5512,7 +5731,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>90538.5078125</v>
+        <v>5955.60595703125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
@@ -5524,7 +5743,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>119213.4921875</v>
+        <v>23275.771484375</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -5536,7 +5755,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>102652.8359375</v>
+        <v>4753.92431640625</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
@@ -5548,7 +5767,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>76029.9609375</v>
+        <v>3248.32885742188</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -5560,11 +5779,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>165324.015625</v>
+        <v>135894.890625</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>8854.3156763353618</v>
+        <v>98479.339398903685</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -5580,11 +5799,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>189902.265625</v>
+        <v>152817.578125</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>33432.565676335362</v>
+        <v>115402.02689890368</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -5600,11 +5819,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>174142.65625</v>
+        <v>150685.15625</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>17672.956301335362</v>
+        <v>113269.60502390368</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -5620,11 +5839,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>200697.03125</v>
+        <v>122257.328125</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>44227.331301335362</v>
+        <v>84841.776898903685</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -5640,11 +5859,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>196633.375</v>
+        <v>126132.1953125</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>40163.675051335362</v>
+        <v>88716.644086403685</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -5660,11 +5879,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>205772.234375</v>
+        <v>124954.375</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>49302.534426335362</v>
+        <v>87538.823773903685</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -5680,11 +5899,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>155182.109375</v>
+        <v>101616.5859375</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-1287.5905736646382</v>
+        <v>64201.034711403678</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -5692,7 +5911,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5700,11 +5919,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>166520.25</v>
+        <v>110730.0859375</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>10050.550051335362</v>
+        <v>73314.534711403685</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -5722,7 +5941,13 @@
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>87.5</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>83036.461219200719</v>
       </c>
     </row>
   </sheetData>
@@ -5731,8 +5956,8 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C61A7656-548B-4995-87CD-0D0D8FF30CE7}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6E3AAB-A9FF-4EF4-B2AE-EECC63B983AA}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5754,11 +5979,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>17152.169921875</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5766,11 +5991,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>5955.60595703125</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5778,11 +6003,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>23275.771484375</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5790,11 +6015,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>4753.92431640625</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5802,11 +6027,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>3248.32885742188</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5814,11 +6039,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>135894.890625</v>
+        <v>91456.8515625</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>98479.339398903685</v>
+        <v>91456.8515625</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -5834,11 +6059,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>152817.578125</v>
+        <v>94876.3984375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>115402.02689890368</v>
+        <v>94876.3984375</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -5854,11 +6079,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>150685.15625</v>
+        <v>109104.921875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>113269.60502390368</v>
+        <v>109104.921875</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -5874,11 +6099,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>122257.328125</v>
+        <v>98020.703125</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>84841.776898903685</v>
+        <v>98020.703125</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -5894,11 +6119,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>126132.1953125</v>
+        <v>94359.8671875</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>88716.644086403685</v>
+        <v>94359.8671875</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -5914,11 +6139,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>124954.375</v>
+        <v>94929.2421875</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>87538.823773903685</v>
+        <v>94929.2421875</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -5934,11 +6159,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>101616.5859375</v>
+        <v>74534.40625</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>64201.034711403678</v>
+        <v>74534.40625</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -5954,11 +6179,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>110730.0859375</v>
+        <v>75661.1875</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>73314.534711403685</v>
+        <v>75661.1875</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -5972,11 +6197,17 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>100</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>56380.275240384617</v>
       </c>
     </row>
   </sheetData>
@@ -5985,8 +6216,8 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6E3AAB-A9FF-4EF4-B2AE-EECC63B983AA}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2CD702F-DB95-45C9-A7DC-43D4DD61B859}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -6008,11 +6239,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>301887.46875</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -6020,11 +6251,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>305612.21875</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -6032,11 +6263,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>324150.84375</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -6044,11 +6275,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>326864.15625</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -6056,11 +6287,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>308804.53125</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6068,11 +6299,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>91456.8515625</v>
+        <v>267728.21875</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>91456.8515625</v>
+        <v>-79648.565351597557</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -6080,7 +6311,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -6088,11 +6319,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>94876.3984375</v>
+        <v>283595.59375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>94876.3984375</v>
+        <v>-63781.190351597557</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -6100,7 +6331,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -6108,11 +6339,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>109104.921875</v>
+        <v>291409.71875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>109104.921875</v>
+        <v>-55967.065351597557</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -6120,7 +6351,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -6128,11 +6359,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>98020.703125</v>
+        <v>399029.3125</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>98020.703125</v>
+        <v>51652.528398402443</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -6148,11 +6379,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>94359.8671875</v>
+        <v>402732.09375</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>94359.8671875</v>
+        <v>55355.309648402443</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -6168,11 +6399,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>94929.2421875</v>
+        <v>415069.1875</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>94929.2421875</v>
+        <v>67692.403398402443</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -6188,11 +6419,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>74534.40625</v>
+        <v>360931.28125</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>74534.40625</v>
+        <v>13554.497148402443</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -6208,11 +6439,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>75661.1875</v>
+        <v>358163.28125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>75661.1875</v>
+        <v>10786.497148402443</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -6226,11 +6457,17 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>61.53846153846154</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>100</v>
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>334305.99278846156</v>
       </c>
     </row>
   </sheetData>
@@ -6239,8 +6476,8 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2CD702F-DB95-45C9-A7DC-43D4DD61B859}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6AA2114-9CC7-4FFF-B55E-10618BA9BC61}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -6262,7 +6499,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>301887.46875</v>
+        <v>396868.375</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
@@ -6274,7 +6511,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>305612.21875</v>
+        <v>415254.03125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
@@ -6286,7 +6523,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>324150.84375</v>
+        <v>417998.125</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -6298,7 +6535,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>326864.15625</v>
+        <v>461263.96875</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
@@ -6310,7 +6547,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>308804.53125</v>
+        <v>410883.0625</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -6322,11 +6559,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>267728.21875</v>
+        <v>267855.625</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-79648.565351597557</v>
+        <v>-225257.50810915342</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -6342,11 +6579,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>283595.59375</v>
+        <v>283538.5</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-63781.190351597557</v>
+        <v>-209574.63310915342</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -6362,11 +6599,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>291409.71875</v>
+        <v>294003.78125</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-55967.065351597557</v>
+        <v>-199109.35185915342</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -6382,11 +6619,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>399029.3125</v>
+        <v>475754.34375</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>51652.528398402443</v>
+        <v>-17358.789359153423</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -6394,7 +6631,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -6402,11 +6639,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>402732.09375</v>
+        <v>467018.25</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>55355.309648402443</v>
+        <v>-26094.883109153423</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -6414,7 +6651,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -6422,11 +6659,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>415069.1875</v>
+        <v>489321.4375</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>67692.403398402443</v>
+        <v>-3791.695609153423</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -6434,7 +6671,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -6442,11 +6679,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>360931.28125</v>
+        <v>429151.4375</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>13554.497148402443</v>
+        <v>-63961.695609153423</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -6454,7 +6691,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -6462,11 +6699,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>358163.28125</v>
+        <v>409255.90625</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>10786.497148402443</v>
+        <v>-83857.226859153423</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -6474,7 +6711,7 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -6484,7 +6721,13 @@
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>62.5</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>401397.44951923075</v>
       </c>
     </row>
   </sheetData>
@@ -6494,7 +6737,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942C0E3F-3149-4A09-BBA8-C13108F7F6F1}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -6932,14 +7175,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>812.99585430438697</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6AA2114-9CC7-4FFF-B55E-10618BA9BC61}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4025ADD-E692-4E9B-BF44-A7A22DF69FFD}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -6961,7 +7210,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>396868.375</v>
+        <v>437221.5</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
@@ -6973,7 +7222,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>415254.03125</v>
+        <v>426584.125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
@@ -6985,7 +7234,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>417998.125</v>
+        <v>417123.96875</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -6997,7 +7246,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>461263.96875</v>
+        <v>495585.375</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
@@ -7009,7 +7258,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>410883.0625</v>
+        <v>383140.6875</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -7021,11 +7270,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>267855.625</v>
+        <v>258072.6875</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-225257.50810915342</v>
+        <v>-296713.85285579215</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -7041,11 +7290,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>283538.5</v>
+        <v>280129.25</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-209574.63310915342</v>
+        <v>-274657.29035579215</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -7061,11 +7310,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>294003.78125</v>
+        <v>275756.5625</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-199109.35185915342</v>
+        <v>-279029.97785579215</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -7081,11 +7330,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>475754.34375</v>
+        <v>425986.25</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-17358.789359153423</v>
+        <v>-128800.29035579215</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -7101,11 +7350,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>467018.25</v>
+        <v>422230.40625</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-26094.883109153423</v>
+        <v>-132556.13410579215</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -7121,11 +7370,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>489321.4375</v>
+        <v>434347.6875</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-3791.695609153423</v>
+        <v>-120438.85285579215</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -7141,11 +7390,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>429151.4375</v>
+        <v>323844.8125</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-63961.695609153423</v>
+        <v>-230941.72785579215</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -7161,11 +7410,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>409255.90625</v>
+        <v>346926.5625</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-83857.226859153423</v>
+        <v>-207859.97785579215</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -7184,6 +7433,12 @@
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>378996.14423076925</v>
       </c>
     </row>
   </sheetData>
@@ -7192,8 +7447,8 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4025ADD-E692-4E9B-BF44-A7A22DF69FFD}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBEACEF-C31B-4520-BB8D-9BD352F73449}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7215,11 +7470,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>437221.5</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7227,11 +7482,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>426584.125</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -7239,11 +7494,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>417123.96875</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -7251,11 +7506,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>495585.375</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7263,11 +7518,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>383140.6875</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7275,11 +7530,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>258072.6875</v>
+        <v>526961.9375</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-296713.85285579215</v>
+        <v>526961.9375</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -7287,7 +7542,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -7295,11 +7550,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>280129.25</v>
+        <v>567003.0625</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-274657.29035579215</v>
+        <v>567003.0625</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -7307,7 +7562,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -7315,11 +7570,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>275756.5625</v>
+        <v>544279.4375</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-279029.97785579215</v>
+        <v>544279.4375</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -7327,7 +7582,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -7335,11 +7590,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>425986.25</v>
+        <v>562823.3125</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-128800.29035579215</v>
+        <v>562823.3125</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -7347,7 +7602,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -7355,11 +7610,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>422230.40625</v>
+        <v>568825.75</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-132556.13410579215</v>
+        <v>568825.75</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -7367,7 +7622,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -7375,11 +7630,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>434347.6875</v>
+        <v>573004.1875</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-120438.85285579215</v>
+        <v>573004.1875</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -7387,7 +7642,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -7395,11 +7650,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>323844.8125</v>
+        <v>458492.1875</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-230941.72785579215</v>
+        <v>458492.1875</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -7407,7 +7662,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -7415,11 +7670,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>346926.5625</v>
+        <v>483568.53125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-207859.97785579215</v>
+        <v>483568.53125</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -7427,17 +7682,23 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>100</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>0</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>329612.18509615387</v>
       </c>
     </row>
   </sheetData>
@@ -7446,8 +7707,8 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBEACEF-C31B-4520-BB8D-9BD352F73449}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A939E7-1E6C-4418-AD0B-19BDD32B1F7A}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7469,11 +7730,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>219022.5</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7481,11 +7742,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>170574.703125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -7493,11 +7754,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>135890.40625</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -7505,11 +7766,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>138744.1875</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7517,11 +7778,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>112022.8984375</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7529,11 +7790,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>526961.9375</v>
+        <v>148701.03125</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>526961.9375</v>
+        <v>-130403.0130752424</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -7541,7 +7802,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -7549,11 +7810,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>567003.0625</v>
+        <v>158603.9375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>567003.0625</v>
+        <v>-120500.1068252424</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -7561,7 +7822,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -7569,11 +7830,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>544279.4375</v>
+        <v>158604.625</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>544279.4375</v>
+        <v>-120499.4193252424</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -7581,7 +7842,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -7589,11 +7850,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>562823.3125</v>
+        <v>195174.96875</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>562823.3125</v>
+        <v>-83929.075575242401</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -7601,7 +7862,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -7609,11 +7870,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>568825.75</v>
+        <v>206578.578125</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>568825.75</v>
+        <v>-72525.466200242401</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -7621,7 +7882,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -7629,11 +7890,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>573004.1875</v>
+        <v>208988.828125</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>573004.1875</v>
+        <v>-70115.216200242401</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -7641,7 +7902,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -7649,11 +7910,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>458492.1875</v>
+        <v>163025.5625</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>458492.1875</v>
+        <v>-116078.4818252424</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -7661,7 +7922,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -7669,11 +7930,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>483568.53125</v>
+        <v>170384.828125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>483568.53125</v>
+        <v>-108719.2162002424</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -7681,17 +7942,23 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>61.53846153846154</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>100</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>168178.23497596153</v>
       </c>
     </row>
   </sheetData>
@@ -7700,8 +7967,8 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A939E7-1E6C-4418-AD0B-19BDD32B1F7A}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AA29FB-8BBF-4EA6-A579-13A41474DE88}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7723,7 +7990,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>219022.5</v>
+        <v>131899.28125</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
@@ -7735,7 +8002,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>170574.703125</v>
+        <v>94481.0078125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
@@ -7747,7 +8014,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>135890.40625</v>
+        <v>72485.0390625</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -7759,7 +8026,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>138744.1875</v>
+        <v>62117.51953125</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
@@ -7771,7 +8038,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>112022.8984375</v>
+        <v>51465.9453125</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -7783,11 +8050,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>148701.03125</v>
+        <v>125120.203125</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-130403.0130752424</v>
+        <v>-52978.413103592524</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -7803,11 +8070,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>158603.9375</v>
+        <v>129989.875</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-120500.1068252424</v>
+        <v>-48108.741228592524</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -7823,11 +8090,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>158604.625</v>
+        <v>131371.203125</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-120499.4193252424</v>
+        <v>-46727.413103592524</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -7843,11 +8110,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>195174.96875</v>
+        <v>169113.375</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-83929.075575242401</v>
+        <v>-8985.2412285925238</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -7863,11 +8130,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>206578.578125</v>
+        <v>168262.734375</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-72525.466200242401</v>
+        <v>-9835.8818535925238</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -7883,11 +8150,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>208988.828125</v>
+        <v>171847.15625</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-70115.216200242401</v>
+        <v>-6251.4599785925238</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -7903,11 +8170,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>163025.5625</v>
+        <v>131469.546875</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-116078.4818252424</v>
+        <v>-46629.069353592524</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -7923,11 +8190,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>170384.828125</v>
+        <v>146564.125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-108719.2162002424</v>
+        <v>-31534.491228592524</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -7946,6 +8213,12 @@
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>122014.38551682692</v>
       </c>
     </row>
   </sheetData>
@@ -7954,8 +8227,8 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AA29FB-8BBF-4EA6-A579-13A41474DE88}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6C4871B-9883-459F-A739-FCC6C13F8FA3}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7977,11 +8250,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>131899.28125</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7989,11 +8262,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>94481.0078125</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8001,11 +8274,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>72485.0390625</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -8013,11 +8286,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>62117.51953125</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -8025,11 +8298,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>51465.9453125</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8037,11 +8310,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>125120.203125</v>
+        <v>187706.484375</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-52978.413103592524</v>
+        <v>187706.484375</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -8049,7 +8322,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -8057,11 +8330,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>129989.875</v>
+        <v>205587.578125</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-48108.741228592524</v>
+        <v>205587.578125</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -8069,7 +8342,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -8077,11 +8350,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>131371.203125</v>
+        <v>209853.921875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-46727.413103592524</v>
+        <v>209853.921875</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -8089,7 +8362,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -8097,11 +8370,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>169113.375</v>
+        <v>155630.609375</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-8985.2412285925238</v>
+        <v>155630.609375</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -8109,7 +8382,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -8117,11 +8390,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>168262.734375</v>
+        <v>158113.703125</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-9835.8818535925238</v>
+        <v>158113.703125</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -8129,7 +8402,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -8137,11 +8410,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>171847.15625</v>
+        <v>166474.453125</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-6251.4599785925238</v>
+        <v>166474.453125</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -8149,7 +8422,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -8157,11 +8430,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>131469.546875</v>
+        <v>108940.796875</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-46629.069353592524</v>
+        <v>108940.796875</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -8169,7 +8442,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -8177,11 +8450,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>146564.125</v>
+        <v>114649.5703125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-31534.491228592524</v>
+        <v>114649.5703125</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -8189,17 +8462,23 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>100</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>0</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>100535.16286057692</v>
       </c>
     </row>
   </sheetData>
@@ -8208,8 +8487,8 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6C4871B-9883-459F-A739-FCC6C13F8FA3}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A280641A-1897-4727-B1AE-AC33B1EDBECC}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -8243,11 +8522,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>3545.08740234375</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8255,11 +8534,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>4456.2578125</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -8291,11 +8570,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>187706.484375</v>
+        <v>4071.96508789063</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>187706.484375</v>
+        <v>-4172.7407256164515</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -8303,7 +8582,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -8311,11 +8590,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>205587.578125</v>
+        <v>3801.958984375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>205587.578125</v>
+        <v>-4442.746829132082</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -8323,7 +8602,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -8331,11 +8610,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>209853.921875</v>
+        <v>5507.90771484375</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>209853.921875</v>
+        <v>-2736.798098663332</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -8343,7 +8622,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -8351,11 +8630,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>155630.609375</v>
+        <v>11862.3447265625</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>155630.609375</v>
+        <v>3617.638913055418</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -8371,11 +8650,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>158113.703125</v>
+        <v>10569.361328125</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>158113.703125</v>
+        <v>2324.655514617918</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -8391,19 +8670,19 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>166474.453125</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>166474.453125</v>
+        <v>-8244.705813507082</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -8411,19 +8690,19 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>108940.796875</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>108940.796875</v>
+        <v>-8244.705813507082</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -8431,11 +8710,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>114649.5703125</v>
+        <v>5866.3212890625</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>114649.5703125</v>
+        <v>-2378.384524444582</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -8443,7 +8722,7 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -8453,7 +8732,13 @@
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>100</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>3821.6311035156255</v>
       </c>
     </row>
   </sheetData>
@@ -8462,8 +8747,8 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A280641A-1897-4727-B1AE-AC33B1EDBECC}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C4A2D4D-F8BC-42E6-BE96-4564CFFDEC00}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -8497,11 +8782,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>3545.08740234375</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8509,11 +8794,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>4456.2578125</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -8545,11 +8830,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>4071.96508789063</v>
+        <v>115085.546875</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-4172.7407256164515</v>
+        <v>115085.546875</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -8557,7 +8842,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -8565,11 +8850,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>3801.958984375</v>
+        <v>137038.75</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-4442.746829132082</v>
+        <v>137038.75</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -8577,7 +8862,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -8585,11 +8870,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>5507.90771484375</v>
+        <v>134307.609375</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-2736.798098663332</v>
+        <v>134307.609375</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -8597,7 +8882,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -8605,11 +8890,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>11862.3447265625</v>
+        <v>113133.140625</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>3617.638913055418</v>
+        <v>113133.140625</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -8625,11 +8910,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>10569.361328125</v>
+        <v>102428.7265625</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>2324.655514617918</v>
+        <v>102428.7265625</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -8645,19 +8930,19 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>113548.4609375</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-8244.705813507082</v>
+        <v>113548.4609375</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -8665,19 +8950,19 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>58813.34375</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-8244.705813507082</v>
+        <v>58813.34375</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -8685,11 +8970,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>5866.3212890625</v>
+        <v>67950.8125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-2378.384524444582</v>
+        <v>67950.8125</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -8697,7 +8982,7 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -8707,7 +8992,13 @@
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>25</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>64792.799278846156</v>
       </c>
     </row>
   </sheetData>
@@ -8716,8 +9007,8 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C4A2D4D-F8BC-42E6-BE96-4564CFFDEC00}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF65BE3-5705-4ABA-B6DB-9780587838AA}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -8775,11 +9066,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2251.69873046875</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -8799,11 +9090,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>115085.546875</v>
+        <v>8520.853515625</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>115085.546875</v>
+        <v>5049.542913824389</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -8819,11 +9110,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>137038.75</v>
+        <v>9839.67578125</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>137038.75</v>
+        <v>6368.365179449389</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -8839,11 +9130,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>134307.609375</v>
+        <v>9528.3984375</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>134307.609375</v>
+        <v>6057.087835699389</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -8859,11 +9150,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>113133.140625</v>
+        <v>15834.44140625</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>113133.140625</v>
+        <v>12363.130804449389</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -8879,11 +9170,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>102428.7265625</v>
+        <v>16266.830078125</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>102428.7265625</v>
+        <v>12795.519476324389</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -8899,11 +9190,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>113548.4609375</v>
+        <v>14146.36328125</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>113548.4609375</v>
+        <v>10675.052679449389</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -8919,11 +9210,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>58813.34375</v>
+        <v>9458.890625</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>58813.34375</v>
+        <v>5987.580023199389</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -8939,11 +9230,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>67950.8125</v>
+        <v>10842.1416015625</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>67950.8125</v>
+        <v>7370.830999761889</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -8957,11 +9248,17 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>61.53846153846154</v>
+        <v>69.230769230769226</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>7437.6379582331729</v>
       </c>
     </row>
   </sheetData>
@@ -8970,8 +9267,8 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF65BE3-5705-4ABA-B6DB-9780587838AA}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21609D0F-1D77-4F49-A66E-58A7EFF8AA53}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -9029,260 +9326,6 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2251.69873046875</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>8520.853515625</v>
-      </c>
-      <c r="C7">
-        <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>5049.542913824389</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>9839.67578125</v>
-      </c>
-      <c r="C8">
-        <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>6368.365179449389</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>9528.3984375</v>
-      </c>
-      <c r="C9">
-        <f t="shared" si="1"/>
-        <v>6057.087835699389</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>15834.44140625</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="1"/>
-        <v>12363.130804449389</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>16266.830078125</v>
-      </c>
-      <c r="C11">
-        <f t="shared" si="1"/>
-        <v>12795.519476324389</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>14146.36328125</v>
-      </c>
-      <c r="C12">
-        <f t="shared" si="1"/>
-        <v>10675.052679449389</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>9458.890625</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="1"/>
-        <v>5987.580023199389</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>10842.1416015625</v>
-      </c>
-      <c r="C14">
-        <f t="shared" si="1"/>
-        <v>7370.830999761889</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>69.230769230769226</v>
-      </c>
-      <c r="E16">
-        <f>SUM(E7:E14)/8 * 100</f>
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21609D0F-1D77-4F49-A66E-58A7EFF8AA53}">
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
         <v>0</v>
       </c>
       <c r="D5">
@@ -9470,6 +9513,12 @@
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>1827.4127385066115</v>
       </c>
     </row>
   </sheetData>
@@ -9479,7 +9528,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27C0A233-0877-46CB-80DD-CCFBB9A1DEF6}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -9724,6 +9773,12 @@
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>7025.7919170673076</v>
       </c>
     </row>
   </sheetData>
@@ -9733,7 +9788,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E71F8FCF-525D-4085-91E8-CF028F81EB85}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -9983,6 +10038,12 @@
         <v>100</v>
       </c>
     </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>595234.8125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9990,7 +10051,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEABF0AE-28FB-4E17-ABF0-B26A56E33970}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -10235,6 +10296,12 @@
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>68730.022235576922</v>
       </c>
     </row>
   </sheetData>
@@ -10244,7 +10311,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4310F7-F432-4C06-AE6D-4EA24129CE24}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -10489,6 +10556,12 @@
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>2446575.451923077</v>
       </c>
     </row>
   </sheetData>
@@ -10745,7 +10818,13 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>3572.077204777645</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -10757,7 +10836,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D08145B-C46C-4C93-88A6-B52C646370D6}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11004,6 +11083,12 @@
         <v>100</v>
       </c>
     </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B2:B14)</f>
+        <v>47056.896033653844</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PIMMS Validation work/Skyline comparison data/Skyline_all_analyte_detection_frequency.xlsx
+++ b/PIMMS Validation work/Skyline comparison data/Skyline_all_analyte_detection_frequency.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\PFAS-IMplementor-for-Mass-Spectrometry--PIMMS-\PIMMS Validation work\Skyline comparison data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0C796A-5DA8-4F52-A5BF-2FFA8A8F0C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFE25CF-3AD2-400E-9127-5852F575A333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79560FBE-CED3-4771-A659-93F59127F910}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="32" activeTab="36" xr2:uid="{79560FBE-CED3-4771-A659-93F59127F910}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="41" r:id="rId1"/>
@@ -18,39 +18,38 @@
     <sheet name="PFPeS - Native" sheetId="2" r:id="rId3"/>
     <sheet name="PFHxS - Branched Native" sheetId="3" r:id="rId4"/>
     <sheet name="PFHxS - Linear Native" sheetId="4" r:id="rId5"/>
-    <sheet name="PFHxS Heavy 402" sheetId="5" r:id="rId6"/>
-    <sheet name="PFHxS Heavy 401" sheetId="6" r:id="rId7"/>
-    <sheet name="PFECHS UPFOS" sheetId="7" r:id="rId8"/>
-    <sheet name="PFHpS - Linear Native" sheetId="8" r:id="rId9"/>
-    <sheet name="PFHpS - Branched Native" sheetId="9" r:id="rId10"/>
-    <sheet name="PFOS - Linear Native" sheetId="10" r:id="rId11"/>
-    <sheet name="PFOS - Branched Native" sheetId="11" r:id="rId12"/>
-    <sheet name="PFOS - Heavy" sheetId="12" r:id="rId13"/>
-    <sheet name="PFDS - Linear Native" sheetId="14" r:id="rId14"/>
-    <sheet name="PFHxA - Heavy" sheetId="15" r:id="rId15"/>
-    <sheet name="PFHpA - Native" sheetId="16" r:id="rId16"/>
-    <sheet name="PFHpA - Heavy" sheetId="17" r:id="rId17"/>
-    <sheet name="PFOA - Branched Native" sheetId="18" r:id="rId18"/>
-    <sheet name="PFOA - Linear Native" sheetId="19" r:id="rId19"/>
-    <sheet name="PFOA - Linear Heavy" sheetId="20" r:id="rId20"/>
-    <sheet name="PFNA - Linear Native" sheetId="21" r:id="rId21"/>
-    <sheet name="PFNA - Heavy" sheetId="22" r:id="rId22"/>
-    <sheet name="PFDA - Linear Native" sheetId="23" r:id="rId23"/>
-    <sheet name="PFDA - Heavy" sheetId="24" r:id="rId24"/>
-    <sheet name="PFUdA - Heavy" sheetId="25" r:id="rId25"/>
-    <sheet name="PFDoA - Heavy" sheetId="26" r:id="rId26"/>
-    <sheet name="PFTeDA - Heavy" sheetId="27" r:id="rId27"/>
-    <sheet name="42 FTS - Heavy" sheetId="28" r:id="rId28"/>
-    <sheet name="62 FTS - Heavy" sheetId="29" r:id="rId29"/>
-    <sheet name="82 FTS - Heavy" sheetId="30" r:id="rId30"/>
-    <sheet name="FOSA - Heavy" sheetId="31" r:id="rId31"/>
-    <sheet name="NMeFOSAA - Heavy" sheetId="33" r:id="rId32"/>
-    <sheet name="NEtFOSAA - Heavy" sheetId="34" r:id="rId33"/>
-    <sheet name="NMeFOSA - Heavy " sheetId="35" r:id="rId34"/>
-    <sheet name="NMeFOSA - Heavy smaller peak" sheetId="36" r:id="rId35"/>
-    <sheet name="NEtFOSA - Heavy" sheetId="37" r:id="rId36"/>
-    <sheet name="NEtFOSA - Heavy smaller peak" sheetId="38" r:id="rId37"/>
-    <sheet name="HFPO-DA Heavy" sheetId="40" r:id="rId38"/>
+    <sheet name="PFHxS Heavy 401" sheetId="6" r:id="rId6"/>
+    <sheet name="PFECHS UPFOS" sheetId="7" r:id="rId7"/>
+    <sheet name="PFHpS - Linear Native" sheetId="8" r:id="rId8"/>
+    <sheet name="PFHpS - Branched Native" sheetId="9" r:id="rId9"/>
+    <sheet name="PFOS - Linear Native" sheetId="10" r:id="rId10"/>
+    <sheet name="PFOS - Branched Native" sheetId="11" r:id="rId11"/>
+    <sheet name="PFOS - Heavy" sheetId="12" r:id="rId12"/>
+    <sheet name="PFDS - Linear Native" sheetId="14" r:id="rId13"/>
+    <sheet name="PFHxA - Heavy" sheetId="15" r:id="rId14"/>
+    <sheet name="PFHpA - Native" sheetId="16" r:id="rId15"/>
+    <sheet name="PFHpA - Heavy" sheetId="17" r:id="rId16"/>
+    <sheet name="PFOA - Branched Native" sheetId="18" r:id="rId17"/>
+    <sheet name="PFOA - Linear Native" sheetId="19" r:id="rId18"/>
+    <sheet name="PFOA - Linear Heavy" sheetId="20" r:id="rId19"/>
+    <sheet name="PFNA - Linear Native" sheetId="21" r:id="rId20"/>
+    <sheet name="PFNA - Heavy" sheetId="22" r:id="rId21"/>
+    <sheet name="PFDA - Linear Native" sheetId="23" r:id="rId22"/>
+    <sheet name="PFDA - Heavy" sheetId="24" r:id="rId23"/>
+    <sheet name="PFUdA - Heavy" sheetId="25" r:id="rId24"/>
+    <sheet name="PFDoA - Heavy" sheetId="26" r:id="rId25"/>
+    <sheet name="PFTeDA - Heavy" sheetId="27" r:id="rId26"/>
+    <sheet name="42 FTS - Heavy" sheetId="28" r:id="rId27"/>
+    <sheet name="62 FTS - Heavy" sheetId="29" r:id="rId28"/>
+    <sheet name="82 FTS - Heavy" sheetId="30" r:id="rId29"/>
+    <sheet name="FOSA - Heavy" sheetId="31" r:id="rId30"/>
+    <sheet name="NMeFOSAA - Heavy" sheetId="33" r:id="rId31"/>
+    <sheet name="NEtFOSAA - Heavy" sheetId="34" r:id="rId32"/>
+    <sheet name="NMeFOSA - Heavy " sheetId="35" r:id="rId33"/>
+    <sheet name="NMeFOSA - Heavy smaller peak" sheetId="36" r:id="rId34"/>
+    <sheet name="NEtFOSA - Heavy" sheetId="37" r:id="rId35"/>
+    <sheet name="NEtFOSA - Heavy smaller peak" sheetId="38" r:id="rId36"/>
+    <sheet name="HFPO-DA Heavy" sheetId="40" r:id="rId37"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="50">
   <si>
     <t>Method Blank 1</t>
   </si>
@@ -127,27 +126,6 @@
   </si>
   <si>
     <t>Notes: Appears at the top of the drift window with inconsistent positioning. Unable to determine if it is UPFOS or PFECHS</t>
-  </si>
-  <si>
-    <t>idotp</t>
-  </si>
-  <si>
-    <t>precursor - 348.9398[M-H]</t>
-  </si>
-  <si>
-    <t>Replicate</t>
-  </si>
-  <si>
-    <t>Peak Area</t>
-  </si>
-  <si>
-    <t>StdErr</t>
-  </si>
-  <si>
-    <t>Expected</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
   <si>
     <t>Notes</t>
@@ -637,10 +615,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s">
         <v>13</v>
@@ -649,15 +627,15 @@
         <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -671,7 +649,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>46.153846153846153</v>
@@ -685,10 +663,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>61.53846153846154</v>
@@ -702,10 +680,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>61.53846153846154</v>
@@ -719,10 +697,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -736,10 +714,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -753,7 +731,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8">
@@ -768,10 +746,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <v>61.53846153846154</v>
@@ -785,10 +763,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>30.76923076923077</v>
@@ -802,10 +780,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>76.923076923076934</v>
@@ -819,10 +797,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>61.53846153846154</v>
@@ -836,10 +814,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -853,7 +831,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>23.076923076923077</v>
@@ -867,10 +845,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -884,7 +862,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>53.846153846153847</v>
@@ -898,10 +876,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -915,10 +893,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>53.846153846153847</v>
@@ -932,10 +910,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -949,10 +927,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -966,7 +944,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C21">
         <v>69.230769230769226</v>
@@ -980,10 +958,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -997,7 +975,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C23">
         <v>38.461538461538467</v>
@@ -1011,10 +989,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C24">
         <v>92.307692307692307</v>
@@ -1028,10 +1006,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -1045,10 +1023,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -1062,10 +1040,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C27">
         <v>61.53846153846154</v>
@@ -1079,10 +1057,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -1096,10 +1074,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -1113,10 +1091,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -1130,10 +1108,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C31">
         <v>61.53846153846154</v>
@@ -1147,10 +1125,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -1164,10 +1142,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -1181,10 +1159,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C34">
         <v>61.538461538500002</v>
@@ -1198,10 +1176,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C35">
         <v>61.538461538500002</v>
@@ -1215,10 +1193,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C36">
         <v>61.538461538500002</v>
@@ -1232,10 +1210,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C37">
         <v>69.230769230769226</v>
@@ -1249,10 +1227,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C38">
         <v>46.153846153846153</v>
@@ -1270,8 +1248,8 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3582B0E6-5A5B-4C02-98A3-54931C7DC318}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FC1C3A-F78D-440D-BD66-AE87DD7194BA}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1293,11 +1271,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>22.663446426391602</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1341,11 +1319,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>445.12939453125</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1353,19 +1331,19 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2276538</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>0</v>
+        <v>2275854.1046568602</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1373,19 +1351,19 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2351341</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>0</v>
+        <v>2350657.1046568602</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1393,11 +1371,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2613.88256835938</v>
+        <v>2433654</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>2613.88256835938</v>
+        <v>2432970.1046568602</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -1413,11 +1391,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>6067.1884765625</v>
+        <v>3055142.25</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>6067.1884765625</v>
+        <v>3054458.3546568602</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -1433,11 +1411,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>6112.1142578125</v>
+        <v>3036440</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>6112.1142578125</v>
+        <v>3035756.1046568602</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -1453,11 +1431,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>5914.23291015625</v>
+        <v>3036979</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>5914.23291015625</v>
+        <v>3036295.1046568602</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -1473,19 +1451,19 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>2622149.25</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2621465.3546568602</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1493,35 +1471,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>2763856.5</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2763172.6046568602</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>2697012.5</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>2696328.6046568602</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>30.76923076923077</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>1592.8783240685102</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1530,8 +1510,8 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FC1C3A-F78D-440D-BD66-AE87DD7194BA}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B920CE9E-75B8-4A59-A12E-E0D1E93B39D0}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1553,11 +1533,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>22.663446426391602</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1601,11 +1581,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>445.12939453125</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1613,11 +1593,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2276538</v>
+        <v>1506597</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>2275854.1046568602</v>
+        <v>1506597</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -1633,11 +1613,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2351341</v>
+        <v>1574906.125</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>2350657.1046568602</v>
+        <v>1574906.125</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -1653,11 +1633,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2433654</v>
+        <v>1527947.375</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>2432970.1046568602</v>
+        <v>1527947.375</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -1673,11 +1653,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>3055142.25</v>
+        <v>2347956.5</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>3054458.3546568602</v>
+        <v>2347956.5</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -1693,11 +1673,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>3036440</v>
+        <v>2351610.5</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>3035756.1046568602</v>
+        <v>2351610.5</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -1713,11 +1693,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>3036979</v>
+        <v>2363344.25</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>3036295.1046568602</v>
+        <v>2363344.25</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -1733,11 +1713,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>2622149.25</v>
+        <v>1534288.625</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>2621465.3546568602</v>
+        <v>1534288.625</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -1753,11 +1733,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>2763856.5</v>
+        <v>1472780.125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>2763172.6046568602</v>
+        <v>1472780.125</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -1769,19 +1749,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>1834928.8125</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>1834928.8125</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>76.923076923076934</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>1659735.9840646891</v>
       </c>
     </row>
   </sheetData>
@@ -1790,8 +1772,8 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B920CE9E-75B8-4A59-A12E-E0D1E93B39D0}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8555E29D-7B73-40B6-8CCA-CFFCF19C489C}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1813,11 +1795,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>2696340.5</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1825,11 +1807,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>2669588.5</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1837,11 +1819,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>2507976.5</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1849,11 +1831,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2853058.5</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1861,11 +1843,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2479145</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1873,11 +1855,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>1506597</v>
+        <v>1682276.625</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>1506597</v>
+        <v>-1415745.6089047305</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -1885,7 +1867,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1893,11 +1875,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>1574906.125</v>
+        <v>1716511.875</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>1574906.125</v>
+        <v>-1381510.3589047305</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -1905,7 +1887,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1913,11 +1895,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>1527947.375</v>
+        <v>1745773.75</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>1527947.375</v>
+        <v>-1352248.4839047305</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -1925,7 +1907,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1933,11 +1915,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>2347956.5</v>
+        <v>1863251.25</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>2347956.5</v>
+        <v>-1234770.9839047305</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -1945,7 +1927,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1953,11 +1935,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>2351610.5</v>
+        <v>1872243.625</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>2351610.5</v>
+        <v>-1225778.6089047305</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -1965,7 +1947,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1973,11 +1955,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>2363344.25</v>
+        <v>1864810.25</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>2363344.25</v>
+        <v>-1233211.9839047305</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -1985,7 +1967,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1993,11 +1975,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>1534288.625</v>
+        <v>1661561.5</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>1534288.625</v>
+        <v>-1436460.7339047305</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -2005,7 +1987,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2013,11 +1995,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>1472780.125</v>
+        <v>1676780.75</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>1472780.125</v>
+        <v>-1421241.4839047305</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -2025,23 +2007,25 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>1760401.203125</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>-1337621.0307797305</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>61.53846153846154</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>1129186.9615384615</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2050,8 +2034,8 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8555E29D-7B73-40B6-8CCA-CFFCF19C489C}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F76DF-C21E-4C19-B3CD-AB910E26AFC2}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2073,11 +2057,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>2696340.5</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2085,11 +2069,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2669588.5</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2097,11 +2081,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2507976.5</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2109,11 +2093,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2853058.5</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2121,11 +2105,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2479145</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2133,11 +2117,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>1682276.625</v>
+        <v>4387.17626953125</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-1415745.6089047305</v>
+        <v>4387.17626953125</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -2145,7 +2129,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2153,11 +2137,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>1716511.875</v>
+        <v>5261.6826171875</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-1381510.3589047305</v>
+        <v>5261.6826171875</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -2165,7 +2149,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2173,11 +2157,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>1745773.75</v>
+        <v>2692.7744140625</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-1352248.4839047305</v>
+        <v>2692.7744140625</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -2185,7 +2169,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2193,15 +2177,15 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>1863251.25</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-1234770.9839047305</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
@@ -2213,15 +2197,15 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>1872243.625</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-1225778.6089047305</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
@@ -2233,15 +2217,15 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>1864810.25</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-1233211.9839047305</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
@@ -2253,15 +2237,15 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>1661561.5</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-1436460.7339047305</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
@@ -2273,15 +2257,15 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>1676780.75</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-1421241.4839047305</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
@@ -2289,19 +2273,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>1542.7041625976563</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>1542.7041625976563</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>100</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>37.5</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>2099178.355769231</v>
+        <v>37.5</v>
       </c>
     </row>
   </sheetData>
@@ -2310,8 +2296,8 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F76DF-C21E-4C19-B3CD-AB910E26AFC2}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBA0397-8353-463A-882C-3FE22A5D5D75}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2333,11 +2319,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>69798.1015625</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2345,11 +2331,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>68369.4453125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2357,11 +2343,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>66003.2578125</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2369,11 +2355,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>81546.578125</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2381,11 +2367,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>65632.34375</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2393,11 +2379,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>4387.17626953125</v>
+        <v>92055.8828125</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>4387.17626953125</v>
+        <v>2187.5919477746793</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -2413,11 +2399,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>5261.6826171875</v>
+        <v>105429.296875</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>5261.6826171875</v>
+        <v>15561.006010274679</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -2433,11 +2419,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2692.7744140625</v>
+        <v>99373.421875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>2692.7744140625</v>
+        <v>9505.1310102746793</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -2453,15 +2439,15 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>84551.8671875</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-5316.4236772253207</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
@@ -2473,19 +2459,19 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>92856.8046875</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2988.5138227746793</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2493,19 +2479,19 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>92011.265625</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2142.9747602746793</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2513,15 +2499,15 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>79530.109375</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-10338.181489725321</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
@@ -2533,15 +2519,15 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>75180.359375</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-14687.931489725321</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
@@ -2549,19 +2535,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>90123.6259765625</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>255.33511183717928</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>23.076923076923077</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>949.35640775240381</v>
+        <v>62.5</v>
       </c>
     </row>
   </sheetData>
@@ -2570,8 +2558,8 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBA0397-8353-463A-882C-3FE22A5D5D75}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C066AFD-AB72-49D4-8676-B34BA24294E8}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2593,11 +2581,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>69798.1015625</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2605,11 +2593,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>68369.4453125</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2617,11 +2605,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>66003.2578125</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2629,11 +2617,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>81546.578125</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2641,11 +2629,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>65632.34375</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2653,11 +2641,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>92055.8828125</v>
+        <v>6431.6748046875</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>2187.5919477746793</v>
+        <v>6431.6748046875</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -2673,11 +2661,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>105429.296875</v>
+        <v>9010.33984375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>15561.006010274679</v>
+        <v>9010.33984375</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -2693,11 +2681,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>99373.421875</v>
+        <v>8583.357421875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>9505.1310102746793</v>
+        <v>8583.357421875</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -2713,11 +2701,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>84551.8671875</v>
+        <v>3210.9296875</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-5316.4236772253207</v>
+        <v>3210.9296875</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -2725,7 +2713,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2733,11 +2721,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>92856.8046875</v>
+        <v>4768.36865234375</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>2988.5138227746793</v>
+        <v>4768.36865234375</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -2753,11 +2741,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>92011.265625</v>
+        <v>5185.181640625</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>2142.9747602746793</v>
+        <v>5185.181640625</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -2773,11 +2761,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>79530.109375</v>
+        <v>2299.47412109375</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-10338.181489725321</v>
+        <v>2299.47412109375</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -2785,7 +2773,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2793,15 +2781,15 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>75180.359375</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-14687.931489725321</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
@@ -2809,19 +2797,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>4936.165771484375</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>4936.165771484375</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>100</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>87.5</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>62.5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>82487.594951923078</v>
+        <v>87.5</v>
       </c>
     </row>
   </sheetData>
@@ -2830,8 +2820,8 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C066AFD-AB72-49D4-8676-B34BA24294E8}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75A288D7-A45C-4CB7-B512-97C064450FDC}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2853,11 +2843,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>328549.25</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2865,11 +2855,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>349568.15625</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2877,11 +2867,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>344527.125</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2889,11 +2879,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>372575.28125</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2901,11 +2891,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>346503.15625</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2913,11 +2903,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>6431.6748046875</v>
+        <v>382461.84375</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>6431.6748046875</v>
+        <v>-13279.971021820558</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -2925,7 +2915,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2933,11 +2923,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>9010.33984375</v>
+        <v>425844.875</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>9010.33984375</v>
+        <v>30103.060228179442</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -2953,11 +2943,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>8583.357421875</v>
+        <v>416779.125</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>8583.357421875</v>
+        <v>21037.310228179442</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -2973,11 +2963,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>3210.9296875</v>
+        <v>380325.96875</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>3210.9296875</v>
+        <v>-15415.846021820558</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -2985,7 +2975,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2993,11 +2983,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>4768.36865234375</v>
+        <v>382843.09375</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>4768.36865234375</v>
+        <v>-12898.721021820558</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -3005,7 +2995,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -3013,11 +3003,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>5185.181640625</v>
+        <v>415339.1875</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>5185.181640625</v>
+        <v>19597.372728179442</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -3033,11 +3023,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>2299.47412109375</v>
+        <v>373603.625</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>2299.47412109375</v>
+        <v>-22138.189771820558</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -3045,7 +3035,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -3053,15 +3043,15 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>379747.90625</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-15993.908521820558</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
@@ -3069,19 +3059,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>394618.203125</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>-1123.6116468205582</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>53.846153846153847</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>87.5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>3037.6404747596152</v>
+        <v>37.5</v>
       </c>
     </row>
   </sheetData>
@@ -3090,266 +3082,6 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75A288D7-A45C-4CB7-B512-97C064450FDC}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>328549.25</v>
-      </c>
-      <c r="D2">
-        <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>349568.15625</v>
-      </c>
-      <c r="D3">
-        <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>344527.125</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>372575.28125</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>346503.15625</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>382461.84375</v>
-      </c>
-      <c r="C7">
-        <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-13279.971021820558</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>425844.875</v>
-      </c>
-      <c r="C8">
-        <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>30103.060228179442</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>416779.125</v>
-      </c>
-      <c r="C9">
-        <f t="shared" si="1"/>
-        <v>21037.310228179442</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>380325.96875</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="1"/>
-        <v>-15415.846021820558</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>382843.09375</v>
-      </c>
-      <c r="C11">
-        <f t="shared" si="1"/>
-        <v>-12898.721021820558</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>415339.1875</v>
-      </c>
-      <c r="C12">
-        <f t="shared" si="1"/>
-        <v>19597.372728179442</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>373603.625</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="1"/>
-        <v>-22138.189771820558</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>379747.90625</v>
-      </c>
-      <c r="C14">
-        <f t="shared" si="1"/>
-        <v>-15993.908521820558</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>100</v>
-      </c>
-      <c r="E16">
-        <f>SUM(E7:E14)/8 * 100</f>
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>376820.66105769231</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D17BA435-9AAF-482D-99AF-F69269029229}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3609,9 +3341,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B373B079-11F4-48D2-A74B-22D8B71CC3A8}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3849,8 +3581,16 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>312458.77734375</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>305309.88916013954</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
+        <f>SUM(D7:D14)/8 * 100</f>
         <v>100</v>
       </c>
       <c r="E16">
@@ -3858,10 +3598,266 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>193456.36618276744</v>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D90E46-680E-43C5-899C-332D591CDF68}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>626116.5</v>
+      </c>
+      <c r="D2">
+        <f>IF(B2&gt;0, 1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>659753</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>661851.5</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>685317.75</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>653382.125</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>608325.9375</v>
+      </c>
+      <c r="C7">
+        <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
+        <v>-112588.77570361143</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <f>IF(C7&gt;0, 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>641939.3125</v>
+      </c>
+      <c r="C8">
+        <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
+        <v>-78975.400703611434</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>620447.0625</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>-100467.65070361143</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>753973.4375</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>33058.724296388566</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>754605.6875</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>33690.974296388566</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>797468.3125</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="1"/>
+        <v>76553.599296388566</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>679001</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="1"/>
+        <v>-41913.713203611434</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>695017.3125</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="1"/>
+        <v>-25897.400703611434</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>693847.2578125</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>-27067.455391111434</v>
+      </c>
+      <c r="D16">
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <f>SUM(E7:E14)/8 * 100</f>
+        <v>37.5</v>
       </c>
     </row>
   </sheetData>
@@ -3871,7 +3867,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64FBD9A9-81EB-4FCF-9AE1-F11107D115C5}">
-  <dimension ref="G1:K17"/>
+  <dimension ref="B1:K17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -4114,20 +4110,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="J16">
-        <f>SUM(J2:J14)/13 * 100</f>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" t="e">
+        <f>AVERAGE(B7:B14)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C17" t="e">
+        <f>AVERAGE(C7:C14)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D17">
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <f>SUM(E7:E14)/8 * 100</f>
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <f>AVERAGE(H7:H14)</f>
+        <v>1516106.640625</v>
+      </c>
+      <c r="I17">
+        <f>AVERAGE(I7:I14)</f>
+        <v>-260241.82969852979</v>
+      </c>
+      <c r="J17">
+        <f>SUM(J7:J14)/8 * 100</f>
         <v>100</v>
       </c>
-      <c r="K16">
+      <c r="K17">
         <f>SUM(K7:K14)/8 * 100</f>
         <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H17">
-        <f>AVERAGE(H2:H14)</f>
-        <v>1529309.5961538462</v>
       </c>
     </row>
   </sheetData>
@@ -4136,8 +4150,8 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D90E46-680E-43C5-899C-332D591CDF68}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8B39702-5FBC-47D5-A77D-76A613184E77}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4159,11 +4173,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>626116.5</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4171,11 +4185,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>659753</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4183,11 +4197,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>661851.5</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4195,11 +4209,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>685317.75</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4207,7 +4221,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>653382.125</v>
+        <v>59.975738525390597</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -4219,11 +4233,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>608325.9375</v>
+        <v>38310.765625</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-112588.77570361143</v>
+        <v>38218.304580288808</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -4231,7 +4245,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -4239,11 +4253,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>641939.3125</v>
+        <v>39549.5234375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-78975.400703611434</v>
+        <v>39457.062392788808</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -4251,7 +4265,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -4259,11 +4273,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>620447.0625</v>
+        <v>37016.54296875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-100467.65070361143</v>
+        <v>36924.081924038808</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -4271,7 +4285,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4279,11 +4293,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>753973.4375</v>
+        <v>66430.625</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>33058.724296388566</v>
+        <v>66338.163955288808</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -4299,11 +4313,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>754605.6875</v>
+        <v>57609.11328125</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>33690.974296388566</v>
+        <v>57516.652236538808</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -4319,11 +4333,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>797468.3125</v>
+        <v>64442.453125</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>76553.599296388566</v>
+        <v>64349.992080288808</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -4339,11 +4353,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>679001</v>
+        <v>38793.4296875</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-41913.713203611434</v>
+        <v>38700.968642788808</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -4351,7 +4365,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -4359,11 +4373,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>695017.3125</v>
+        <v>36948.4921875</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-25897.400703611434</v>
+        <v>36856.031142788808</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -4371,23 +4385,25 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>47387.6181640625</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>47295.157119351315</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
+        <f>SUM(D7:D14)/8 * 100</f>
         <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>679784.53365384613</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4396,8 +4412,8 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8B39702-5FBC-47D5-A77D-76A613184E77}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3842B4B-8929-4ECB-8BD3-19501EE1AC1C}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4419,11 +4435,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>326238.34375</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4431,11 +4447,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>354287.03125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4443,11 +4459,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>343340.6875</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4455,11 +4471,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>358255.15625</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4467,7 +4483,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>59.975738525390597</v>
+        <v>344247.875</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -4479,11 +4495,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>38310.765625</v>
+        <v>268956.375</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>38218.304580288808</v>
+        <v>-113573.40936318471</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -4491,7 +4507,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -4499,11 +4515,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>39549.5234375</v>
+        <v>266823.15625</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>39457.062392788808</v>
+        <v>-115706.62811318471</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -4511,7 +4527,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -4519,11 +4535,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>37016.54296875</v>
+        <v>243906.234375</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>36924.081924038808</v>
+        <v>-138623.54998818471</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -4531,7 +4547,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4539,11 +4555,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>66430.625</v>
+        <v>354071.0625</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>66338.163955288808</v>
+        <v>-28458.721863184706</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -4551,7 +4567,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -4559,11 +4575,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>57609.11328125</v>
+        <v>363293.71875</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>57516.652236538808</v>
+        <v>-19236.065613184706</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -4571,7 +4587,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -4579,11 +4595,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>64442.453125</v>
+        <v>367311.15625</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>64349.992080288808</v>
+        <v>-15218.628113184706</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -4591,7 +4607,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -4599,11 +4615,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>38793.4296875</v>
+        <v>298605.25</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>38700.968642788808</v>
+        <v>-83924.534363184706</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -4611,7 +4627,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -4619,11 +4635,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>36948.4921875</v>
+        <v>305274.15625</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>36856.031142788808</v>
+        <v>-77255.628113184706</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -4631,23 +4647,25 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>308530.138671875</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>-73999.645691309706</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>69.230769230769226</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>29166.224696232723</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4656,8 +4674,8 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3842B4B-8929-4ECB-8BD3-19501EE1AC1C}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10A91543-3248-43B1-8CC1-89E16ADD1168}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4679,11 +4697,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>326238.34375</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4691,11 +4709,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>354287.03125</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4703,11 +4721,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>343340.6875</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4715,11 +4733,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>358255.15625</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4727,11 +4745,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>344247.875</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4739,11 +4757,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>268956.375</v>
+        <v>5807.3310546875</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-113573.40936318471</v>
+        <v>5807.3310546875</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -4751,7 +4769,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -4759,11 +4777,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>266823.15625</v>
+        <v>4705.115234375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-115706.62811318471</v>
+        <v>4705.115234375</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -4771,7 +4789,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -4779,11 +4797,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>243906.234375</v>
+        <v>7633.1455078125</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-138623.54998818471</v>
+        <v>7633.1455078125</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -4791,7 +4809,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4799,11 +4817,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>354071.0625</v>
+        <v>9279.103515625</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-28458.721863184706</v>
+        <v>9279.103515625</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -4811,7 +4829,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -4819,15 +4837,15 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>363293.71875</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-19236.065613184706</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
@@ -4839,11 +4857,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>367311.15625</v>
+        <v>9098.2724609375</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-15218.628113184706</v>
+        <v>9098.2724609375</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -4851,7 +4869,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -4859,15 +4877,15 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>298605.25</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-83924.534363184706</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
@@ -4879,15 +4897,15 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>305274.15625</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-77255.628113184706</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
@@ -4895,19 +4913,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>4565.3709716796875</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>4565.3709716796875</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>100</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>62.5</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>322662.32331730769</v>
+        <v>62.5</v>
       </c>
     </row>
   </sheetData>
@@ -4916,9 +4936,12 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10A91543-3248-43B1-8CC1-89E16ADD1168}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F62F1E8F-7775-41F2-A9E3-56941E817487}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
@@ -4939,11 +4962,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>245209.03125</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4951,11 +4974,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>240123.96875</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4963,11 +4986,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>264158.40625</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4975,11 +4998,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>276169.4375</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4987,11 +5010,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>243046.46875</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4999,11 +5022,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>5807.3310546875</v>
+        <v>204720.671875</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>5807.3310546875</v>
+        <v>-96077.495010878542</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -5011,7 +5034,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5019,11 +5042,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>4705.115234375</v>
+        <v>208431.9375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>4705.115234375</v>
+        <v>-92366.229385878542</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -5031,7 +5054,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5039,11 +5062,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>7633.1455078125</v>
+        <v>196465.875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>7633.1455078125</v>
+        <v>-104332.29188587854</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -5051,7 +5074,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5059,11 +5082,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>9279.103515625</v>
+        <v>280239.84375</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>9279.103515625</v>
+        <v>-20558.323135878542</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -5071,7 +5094,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5079,15 +5102,15 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>279034.875</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-21763.291885878542</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
@@ -5099,11 +5122,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>9098.2724609375</v>
+        <v>272495.46875</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>9098.2724609375</v>
+        <v>-28302.698135878542</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -5111,7 +5134,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5119,15 +5142,15 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>224961.9375</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-75836.229385878542</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
@@ -5139,15 +5162,15 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>225153.703125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-75644.463760878542</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
@@ -5155,19 +5178,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>236438.0390625</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>-64360.127823378542</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>38.461538461538467</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>62.5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>2809.4590594951924</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5176,8 +5201,8 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F62F1E8F-7775-41F2-A9E3-56941E817487}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A757A9C-A327-434D-82A9-1F401F37251F}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5199,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>245209.03125</v>
+        <v>117939.7109375</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
@@ -5211,7 +5236,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>240123.96875</v>
+        <v>90538.5078125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
@@ -5223,7 +5248,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>264158.40625</v>
+        <v>119213.4921875</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -5235,7 +5260,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>276169.4375</v>
+        <v>102652.8359375</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
@@ -5247,7 +5272,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>243046.46875</v>
+        <v>76029.9609375</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -5259,11 +5284,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>204720.671875</v>
+        <v>165324.015625</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-96077.495010878542</v>
+        <v>8854.3156763353618</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -5271,7 +5296,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5279,11 +5304,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>208431.9375</v>
+        <v>189902.265625</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-92366.229385878542</v>
+        <v>33432.565676335362</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -5291,7 +5316,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5299,11 +5324,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>196465.875</v>
+        <v>174142.65625</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-104332.29188587854</v>
+        <v>17672.956301335362</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -5311,7 +5336,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5319,11 +5344,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>280239.84375</v>
+        <v>200697.03125</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-20558.323135878542</v>
+        <v>44227.331301335362</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -5331,7 +5356,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5339,11 +5364,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>279034.875</v>
+        <v>196633.375</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-21763.291885878542</v>
+        <v>40163.675051335362</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -5351,7 +5376,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5359,11 +5384,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>272495.46875</v>
+        <v>205772.234375</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-28302.698135878542</v>
+        <v>49302.534426335362</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -5371,7 +5396,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5379,11 +5404,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>224961.9375</v>
+        <v>155182.109375</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-75836.229385878542</v>
+        <v>-1287.5905736646382</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -5399,35 +5424,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>166520.25</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-300798.16688587854</v>
+        <v>10050.550051335362</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>181771.7421875</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>25302.042238835362</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>92.307692307692307</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>225773.68629807694</v>
+        <v>87.5</v>
       </c>
     </row>
   </sheetData>
@@ -5436,8 +5463,8 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A757A9C-A327-434D-82A9-1F401F37251F}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C61A7656-548B-4995-87CD-0D0D8FF30CE7}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5459,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>117939.7109375</v>
+        <v>17152.169921875</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
@@ -5471,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>90538.5078125</v>
+        <v>5955.60595703125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
@@ -5483,7 +5510,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>119213.4921875</v>
+        <v>23275.771484375</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -5495,7 +5522,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>102652.8359375</v>
+        <v>4753.92431640625</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
@@ -5507,7 +5534,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>76029.9609375</v>
+        <v>3248.32885742188</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -5519,11 +5546,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>165324.015625</v>
+        <v>135894.890625</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>8854.3156763353618</v>
+        <v>98479.339398903685</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -5539,11 +5566,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>189902.265625</v>
+        <v>152817.578125</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>33432.565676335362</v>
+        <v>115402.02689890368</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -5559,11 +5586,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>174142.65625</v>
+        <v>150685.15625</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>17672.956301335362</v>
+        <v>113269.60502390368</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -5579,11 +5606,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>200697.03125</v>
+        <v>122257.328125</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>44227.331301335362</v>
+        <v>84841.776898903685</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -5599,11 +5626,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>196633.375</v>
+        <v>126132.1953125</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>40163.675051335362</v>
+        <v>88716.644086403685</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -5619,11 +5646,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>205772.234375</v>
+        <v>124954.375</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>49302.534426335362</v>
+        <v>87538.823773903685</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -5639,11 +5666,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>155182.109375</v>
+        <v>101616.5859375</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-1287.5905736646382</v>
+        <v>64201.034711403678</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -5651,7 +5678,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5659,11 +5686,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>166520.25</v>
+        <v>110730.0859375</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>10050.550051335362</v>
+        <v>73314.534711403685</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -5675,19 +5702,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>128136.0244140625</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>90720.47318796617</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
+        <f>SUM(D7:D14)/8 * 100</f>
         <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>87.5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>150811.41887019231</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5696,8 +5725,8 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C61A7656-548B-4995-87CD-0D0D8FF30CE7}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6E3AAB-A9FF-4EF4-B2AE-EECC63B983AA}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5719,11 +5748,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>17152.169921875</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5731,11 +5760,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>5955.60595703125</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5743,11 +5772,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>23275.771484375</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5755,11 +5784,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>4753.92431640625</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5767,11 +5796,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>3248.32885742188</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5779,11 +5808,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>135894.890625</v>
+        <v>91456.8515625</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>98479.339398903685</v>
+        <v>91456.8515625</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -5799,11 +5828,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>152817.578125</v>
+        <v>94876.3984375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>115402.02689890368</v>
+        <v>94876.3984375</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -5819,11 +5848,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>150685.15625</v>
+        <v>109104.921875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>113269.60502390368</v>
+        <v>109104.921875</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -5839,11 +5868,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>122257.328125</v>
+        <v>98020.703125</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>84841.776898903685</v>
+        <v>98020.703125</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -5859,11 +5888,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>126132.1953125</v>
+        <v>94359.8671875</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>88716.644086403685</v>
+        <v>94359.8671875</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -5879,11 +5908,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>124954.375</v>
+        <v>94929.2421875</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>87538.823773903685</v>
+        <v>94929.2421875</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -5899,11 +5928,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>101616.5859375</v>
+        <v>74534.40625</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>64201.034711403678</v>
+        <v>74534.40625</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -5919,11 +5948,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>110730.0859375</v>
+        <v>75661.1875</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>73314.534711403685</v>
+        <v>75661.1875</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -5935,19 +5964,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>91617.947265625</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>91617.947265625</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
+        <f>SUM(D7:D14)/8 * 100</f>
         <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>83036.461219200719</v>
       </c>
     </row>
   </sheetData>
@@ -5956,8 +5987,8 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6E3AAB-A9FF-4EF4-B2AE-EECC63B983AA}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2CD702F-DB95-45C9-A7DC-43D4DD61B859}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5979,11 +6010,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>301887.46875</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5991,11 +6022,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>305612.21875</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -6003,11 +6034,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>324150.84375</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -6015,11 +6046,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>326864.15625</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -6027,11 +6058,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>308804.53125</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6039,11 +6070,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>91456.8515625</v>
+        <v>267728.21875</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>91456.8515625</v>
+        <v>-79648.565351597557</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -6051,7 +6082,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -6059,11 +6090,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>94876.3984375</v>
+        <v>283595.59375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>94876.3984375</v>
+        <v>-63781.190351597557</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -6071,7 +6102,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -6079,11 +6110,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>109104.921875</v>
+        <v>291409.71875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>109104.921875</v>
+        <v>-55967.065351597557</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -6091,7 +6122,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -6099,11 +6130,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>98020.703125</v>
+        <v>399029.3125</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>98020.703125</v>
+        <v>51652.528398402443</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -6119,11 +6150,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>94359.8671875</v>
+        <v>402732.09375</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>94359.8671875</v>
+        <v>55355.309648402443</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -6139,11 +6170,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>94929.2421875</v>
+        <v>415069.1875</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>94929.2421875</v>
+        <v>67692.403398402443</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -6159,11 +6190,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>74534.40625</v>
+        <v>360931.28125</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>74534.40625</v>
+        <v>13554.497148402443</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -6179,11 +6210,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>75661.1875</v>
+        <v>358163.28125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>75661.1875</v>
+        <v>10786.497148402443</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -6195,19 +6226,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>347332.3359375</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>-44.44816409755731</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>61.53846153846154</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>56380.275240384617</v>
+        <v>62.5</v>
       </c>
     </row>
   </sheetData>
@@ -6216,8 +6249,8 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2CD702F-DB95-45C9-A7DC-43D4DD61B859}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6AA2114-9CC7-4FFF-B55E-10618BA9BC61}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -6239,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>301887.46875</v>
+        <v>396868.375</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
@@ -6251,7 +6284,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>305612.21875</v>
+        <v>415254.03125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
@@ -6263,7 +6296,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>324150.84375</v>
+        <v>417998.125</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -6275,7 +6308,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>326864.15625</v>
+        <v>461263.96875</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
@@ -6287,7 +6320,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>308804.53125</v>
+        <v>410883.0625</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -6299,11 +6332,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>267728.21875</v>
+        <v>267855.625</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-79648.565351597557</v>
+        <v>-225257.50810915342</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -6319,11 +6352,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>283595.59375</v>
+        <v>283538.5</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-63781.190351597557</v>
+        <v>-209574.63310915342</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -6339,11 +6372,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>291409.71875</v>
+        <v>294003.78125</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-55967.065351597557</v>
+        <v>-199109.35185915342</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -6359,11 +6392,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>399029.3125</v>
+        <v>475754.34375</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>51652.528398402443</v>
+        <v>-17358.789359153423</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -6371,7 +6404,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -6379,11 +6412,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>402732.09375</v>
+        <v>467018.25</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>55355.309648402443</v>
+        <v>-26094.883109153423</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -6391,7 +6424,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -6399,11 +6432,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>415069.1875</v>
+        <v>489321.4375</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>67692.403398402443</v>
+        <v>-3791.695609153423</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -6411,7 +6444,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -6419,11 +6452,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>360931.28125</v>
+        <v>429151.4375</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>13554.497148402443</v>
+        <v>-63961.695609153423</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -6431,7 +6464,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -6439,11 +6472,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>358163.28125</v>
+        <v>409255.90625</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>10786.497148402443</v>
+        <v>-83857.226859153423</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -6451,23 +6484,25 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>389487.41015625</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>-103625.72295290345</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
+        <f>SUM(D7:D14)/8 * 100</f>
         <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>62.5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>334305.99278846156</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6476,8 +6511,8 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6AA2114-9CC7-4FFF-B55E-10618BA9BC61}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4025ADD-E692-4E9B-BF44-A7A22DF69FFD}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -6499,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>396868.375</v>
+        <v>437221.5</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
@@ -6511,7 +6546,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>415254.03125</v>
+        <v>426584.125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
@@ -6523,7 +6558,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>417998.125</v>
+        <v>417123.96875</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -6535,7 +6570,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>461263.96875</v>
+        <v>495585.375</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
@@ -6547,7 +6582,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>410883.0625</v>
+        <v>383140.6875</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -6559,11 +6594,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>267855.625</v>
+        <v>258072.6875</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-225257.50810915342</v>
+        <v>-296713.85285579215</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -6579,11 +6614,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>283538.5</v>
+        <v>280129.25</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-209574.63310915342</v>
+        <v>-274657.29035579215</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -6599,11 +6634,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>294003.78125</v>
+        <v>275756.5625</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-199109.35185915342</v>
+        <v>-279029.97785579215</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -6619,11 +6654,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>475754.34375</v>
+        <v>425986.25</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-17358.789359153423</v>
+        <v>-128800.29035579215</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -6639,11 +6674,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>467018.25</v>
+        <v>422230.40625</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-26094.883109153423</v>
+        <v>-132556.13410579215</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -6659,11 +6694,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>489321.4375</v>
+        <v>434347.6875</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-3791.695609153423</v>
+        <v>-120438.85285579215</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -6679,11 +6714,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>429151.4375</v>
+        <v>323844.8125</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-63961.695609153423</v>
+        <v>-230941.72785579215</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -6699,11 +6734,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>409255.90625</v>
+        <v>346926.5625</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-83857.226859153423</v>
+        <v>-207859.97785579215</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -6715,19 +6750,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>345911.77734375</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>-208874.76301204221</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
+        <f>SUM(D7:D14)/8 * 100</f>
         <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>401397.44951923075</v>
       </c>
     </row>
   </sheetData>
@@ -6737,7 +6774,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942C0E3F-3149-4A09-BBA8-C13108F7F6F1}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -6746,7 +6783,7 @@
     <col min="5" max="5" width="54.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>15</v>
       </c>
@@ -6759,14 +6796,8 @@
       <c r="E1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6777,20 +6808,8 @@
         <f>IF(B2&gt;0, 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6801,17 +6820,8 @@
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3">
-        <v>2615.32299804688</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -6822,20 +6832,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>0</v>
-      </c>
-      <c r="I4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6846,20 +6844,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -6870,20 +6856,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>2</v>
-      </c>
-      <c r="I6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -6902,20 +6876,8 @@
         <f>IF(C7&gt;0, 1, 0)</f>
         <v>1</v>
       </c>
-      <c r="H7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6934,20 +6896,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -6966,20 +6916,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9">
-        <v>1152.19580078125</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -6998,20 +6936,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10">
-        <v>1756.09729003906</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -7030,20 +6956,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I11" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11">
-        <v>1893.07824707031</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -7062,20 +6976,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H12" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12">
-        <v>636.17120361328102</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -7094,20 +6996,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13">
-        <v>2516.08056640625</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -7126,59 +7016,23 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14">
-        <v>2615.32299804688</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H15" t="s">
-        <v>11</v>
-      </c>
-      <c r="I15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>46.153846153846153</v>
-      </c>
-      <c r="E16">
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>AVERAGE(B7:B14)</f>
+        <v>1321.1182632446289</v>
+      </c>
+      <c r="C17">
+        <f>AVERAGE(C7:C14)</f>
+        <v>1321.1182632446289</v>
+      </c>
+      <c r="D17">
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>75</v>
+      </c>
+      <c r="E17">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>75</v>
-      </c>
-      <c r="H16" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>812.99585430438697</v>
       </c>
     </row>
   </sheetData>
@@ -7187,8 +7041,8 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4025ADD-E692-4E9B-BF44-A7A22DF69FFD}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBEACEF-C31B-4520-BB8D-9BD352F73449}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7210,11 +7064,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>437221.5</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7222,11 +7076,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>426584.125</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -7234,11 +7088,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>417123.96875</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -7246,11 +7100,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>495585.375</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7258,11 +7112,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>383140.6875</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7270,11 +7124,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>258072.6875</v>
+        <v>526961.9375</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-296713.85285579215</v>
+        <v>526961.9375</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -7282,7 +7136,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -7290,11 +7144,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>280129.25</v>
+        <v>567003.0625</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-274657.29035579215</v>
+        <v>567003.0625</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -7302,7 +7156,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -7310,11 +7164,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>275756.5625</v>
+        <v>544279.4375</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-279029.97785579215</v>
+        <v>544279.4375</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -7322,7 +7176,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -7330,11 +7184,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>425986.25</v>
+        <v>562823.3125</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-128800.29035579215</v>
+        <v>562823.3125</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -7342,7 +7196,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -7350,11 +7204,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>422230.40625</v>
+        <v>568825.75</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-132556.13410579215</v>
+        <v>568825.75</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -7362,7 +7216,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -7370,11 +7224,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>434347.6875</v>
+        <v>573004.1875</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-120438.85285579215</v>
+        <v>573004.1875</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -7382,7 +7236,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -7390,11 +7244,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>323844.8125</v>
+        <v>458492.1875</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-230941.72785579215</v>
+        <v>458492.1875</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -7402,7 +7256,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -7410,11 +7264,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>346926.5625</v>
+        <v>483568.53125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-207859.97785579215</v>
+        <v>483568.53125</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -7422,23 +7276,25 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>535619.80078125</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>535619.80078125</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
+        <f>SUM(D7:D14)/8 * 100</f>
         <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>378996.14423076925</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -7447,8 +7303,8 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBEACEF-C31B-4520-BB8D-9BD352F73449}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A939E7-1E6C-4418-AD0B-19BDD32B1F7A}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7470,11 +7326,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>219022.5</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7482,11 +7338,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>170574.703125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -7494,11 +7350,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>135890.40625</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -7506,11 +7362,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>138744.1875</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7518,11 +7374,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>112022.8984375</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7530,11 +7386,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>526961.9375</v>
+        <v>148701.03125</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>526961.9375</v>
+        <v>-130403.0130752424</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -7542,7 +7398,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -7550,11 +7406,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>567003.0625</v>
+        <v>158603.9375</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>567003.0625</v>
+        <v>-120500.1068252424</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -7562,7 +7418,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -7570,11 +7426,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>544279.4375</v>
+        <v>158604.625</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>544279.4375</v>
+        <v>-120499.4193252424</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -7582,7 +7438,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -7590,11 +7446,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>562823.3125</v>
+        <v>195174.96875</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>562823.3125</v>
+        <v>-83929.075575242401</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -7602,7 +7458,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -7610,11 +7466,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>568825.75</v>
+        <v>206578.578125</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>568825.75</v>
+        <v>-72525.466200242401</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -7622,7 +7478,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -7630,11 +7486,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>573004.1875</v>
+        <v>208988.828125</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>573004.1875</v>
+        <v>-70115.216200242401</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -7642,7 +7498,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -7650,11 +7506,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>458492.1875</v>
+        <v>163025.5625</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>458492.1875</v>
+        <v>-116078.4818252424</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -7662,7 +7518,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -7670,11 +7526,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>483568.53125</v>
+        <v>170384.828125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>483568.53125</v>
+        <v>-108719.2162002424</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -7682,23 +7538,25 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>176257.794921875</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>-102846.2494033674</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>61.53846153846154</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>329612.18509615387</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7707,8 +7565,8 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A939E7-1E6C-4418-AD0B-19BDD32B1F7A}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AA29FB-8BBF-4EA6-A579-13A41474DE88}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7730,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>219022.5</v>
+        <v>131899.28125</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
@@ -7742,7 +7600,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>170574.703125</v>
+        <v>94481.0078125</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
@@ -7754,7 +7612,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>135890.40625</v>
+        <v>72485.0390625</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -7766,7 +7624,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>138744.1875</v>
+        <v>62117.51953125</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
@@ -7778,7 +7636,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>112022.8984375</v>
+        <v>51465.9453125</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -7790,11 +7648,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>148701.03125</v>
+        <v>125120.203125</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-130403.0130752424</v>
+        <v>-52978.413103592524</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -7810,11 +7668,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>158603.9375</v>
+        <v>129989.875</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-120500.1068252424</v>
+        <v>-48108.741228592524</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -7830,11 +7688,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>158604.625</v>
+        <v>131371.203125</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-120499.4193252424</v>
+        <v>-46727.413103592524</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -7850,11 +7708,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>195174.96875</v>
+        <v>169113.375</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-83929.075575242401</v>
+        <v>-8985.2412285925238</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -7870,11 +7728,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>206578.578125</v>
+        <v>168262.734375</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-72525.466200242401</v>
+        <v>-9835.8818535925238</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -7890,11 +7748,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>208988.828125</v>
+        <v>171847.15625</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-70115.216200242401</v>
+        <v>-6251.4599785925238</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -7910,11 +7768,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>163025.5625</v>
+        <v>131469.546875</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-116078.4818252424</v>
+        <v>-46629.069353592524</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -7930,11 +7788,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>170384.828125</v>
+        <v>146564.125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-108719.2162002424</v>
+        <v>-31534.491228592524</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -7946,19 +7804,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>146717.27734375</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>-31381.338884842524</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
+        <f>SUM(D7:D14)/8 * 100</f>
         <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>168178.23497596153</v>
       </c>
     </row>
   </sheetData>
@@ -7967,8 +7827,8 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AA29FB-8BBF-4EA6-A579-13A41474DE88}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6C4871B-9883-459F-A739-FCC6C13F8FA3}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7990,11 +7850,11 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>131899.28125</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -8002,11 +7862,11 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>94481.0078125</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8014,11 +7874,11 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>72485.0390625</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -8026,11 +7886,11 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>62117.51953125</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -8038,11 +7898,11 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>51465.9453125</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8050,11 +7910,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>125120.203125</v>
+        <v>187706.484375</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-52978.413103592524</v>
+        <v>187706.484375</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -8062,7 +7922,7 @@
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -8070,11 +7930,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>129989.875</v>
+        <v>205587.578125</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-48108.741228592524</v>
+        <v>205587.578125</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -8082,7 +7942,7 @@
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -8090,11 +7950,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>131371.203125</v>
+        <v>209853.921875</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-46727.413103592524</v>
+        <v>209853.921875</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -8102,7 +7962,7 @@
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -8110,11 +7970,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>169113.375</v>
+        <v>155630.609375</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-8985.2412285925238</v>
+        <v>155630.609375</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -8122,7 +7982,7 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -8130,11 +7990,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>168262.734375</v>
+        <v>158113.703125</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-9835.8818535925238</v>
+        <v>158113.703125</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -8142,7 +8002,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -8150,11 +8010,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>171847.15625</v>
+        <v>166474.453125</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-6251.4599785925238</v>
+        <v>166474.453125</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -8162,7 +8022,7 @@
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -8170,11 +8030,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>131469.546875</v>
+        <v>108940.796875</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-46629.069353592524</v>
+        <v>108940.796875</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -8182,7 +8042,7 @@
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -8190,11 +8050,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>146564.125</v>
+        <v>114649.5703125</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-31534.491228592524</v>
+        <v>114649.5703125</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -8202,23 +8062,25 @@
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>163369.6396484375</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>163369.6396484375</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
+        <f>SUM(D7:D14)/8 * 100</f>
         <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>122014.38551682692</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -8227,266 +8089,6 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6C4871B-9883-459F-A739-FCC6C13F8FA3}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <f>IF(B2&gt;0, 1, 0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>187706.484375</v>
-      </c>
-      <c r="C7">
-        <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>187706.484375</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>205587.578125</v>
-      </c>
-      <c r="C8">
-        <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>205587.578125</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>209853.921875</v>
-      </c>
-      <c r="C9">
-        <f t="shared" si="1"/>
-        <v>209853.921875</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>155630.609375</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="1"/>
-        <v>155630.609375</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>158113.703125</v>
-      </c>
-      <c r="C11">
-        <f t="shared" si="1"/>
-        <v>158113.703125</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>166474.453125</v>
-      </c>
-      <c r="C12">
-        <f t="shared" si="1"/>
-        <v>166474.453125</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>108940.796875</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="1"/>
-        <v>108940.796875</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>114649.5703125</v>
-      </c>
-      <c r="C14">
-        <f t="shared" si="1"/>
-        <v>114649.5703125</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>61.53846153846154</v>
-      </c>
-      <c r="E16">
-        <f>SUM(E7:E14)/8 * 100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>100535.16286057692</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A280641A-1897-4727-B1AE-AC33B1EDBECC}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8746,9 +8348,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C4A2D4D-F8BC-42E6-BE96-4564CFFDEC00}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -8986,19 +8588,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>105288.298828125</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>105288.298828125</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>61.53846153846154</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>64792.799278846156</v>
       </c>
     </row>
   </sheetData>
@@ -9006,7 +8610,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF65BE3-5705-4ABA-B6DB-9780587838AA}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9266,9 +8870,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21609D0F-1D77-4F49-A66E-58A7EFF8AA53}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -9506,19 +9110,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>2969.5457000732436</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>2969.5457000732436</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>46.153846153846153</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>75</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>1827.4127385066115</v>
       </c>
     </row>
   </sheetData>
@@ -9788,10 +9394,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E71F8FCF-525D-4085-91E8-CF028F81EB85}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -10029,19 +9636,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>967256.5703125</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>967256.5703125</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>61.53846153846154</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>595234.8125</v>
       </c>
     </row>
   </sheetData>
@@ -10050,8 +9659,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEABF0AE-28FB-4E17-ABF0-B26A56E33970}">
-  <dimension ref="A1:E17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4310F7-F432-4C06-AE6D-4EA24129CE24}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -10073,7 +9682,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>69599.640625</v>
+        <v>2397313</v>
       </c>
       <c r="D2">
         <f>IF(B2&gt;0, 1, 0)</f>
@@ -10085,7 +9694,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>65527.6015625</v>
+        <v>2445803</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
@@ -10097,7 +9706,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>69683.828125</v>
+        <v>2846578.5</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -10109,7 +9718,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>86616.3984375</v>
+        <v>2701837.75</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
@@ -10121,7 +9730,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>83209.9140625</v>
+        <v>2800271.5</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -10133,11 +9742,11 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>50715.55078125</v>
+        <v>1728319.375</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-52253.060754843158</v>
+        <v>-1526286.8640246154</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -10153,11 +9762,11 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>51991.34765625</v>
+        <v>1747214.75</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-50977.263879843158</v>
+        <v>-1507391.4890246154</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -10173,11 +9782,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>43565.45703125</v>
+        <v>1720155.75</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>-59403.154504843158</v>
+        <v>-1534450.4890246154</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -10193,11 +9802,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>85819.9296875</v>
+        <v>2765517.75</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>-17148.681848593158</v>
+        <v>-489088.48902461538</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -10213,11 +9822,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>86660.9375</v>
+        <v>2788510.25</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>-16307.674036093158</v>
+        <v>-466095.98902461538</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -10233,11 +9842,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>77998.7421875</v>
+        <v>2815612.25</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>-24969.869348593158</v>
+        <v>-438993.98902461538</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -10253,11 +9862,11 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>57350.08984375</v>
+        <v>2519609.75</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>-45618.521692343158</v>
+        <v>-734996.48902461538</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
@@ -10273,11 +9882,11 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>64750.8515625</v>
+        <v>2528737.25</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>-38217.759973593158</v>
+        <v>-725868.98902461538</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
@@ -10289,19 +9898,21 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>2326709.640625</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>-927896.59839961515</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
+        <f>SUM(D7:D14)/8 * 100</f>
         <v>100</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>68730.022235576922</v>
       </c>
     </row>
   </sheetData>
@@ -10310,266 +9921,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4310F7-F432-4C06-AE6D-4EA24129CE24}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>2397313</v>
-      </c>
-      <c r="D2">
-        <f>IF(B2&gt;0, 1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2445803</v>
-      </c>
-      <c r="D3">
-        <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>2846578.5</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>2701837.75</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>2800271.5</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>1728319.375</v>
-      </c>
-      <c r="C7">
-        <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-1526286.8640246154</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <f>IF(C7&gt;0, 1, 0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>1747214.75</v>
-      </c>
-      <c r="C8">
-        <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>-1507391.4890246154</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>1720155.75</v>
-      </c>
-      <c r="C9">
-        <f t="shared" si="1"/>
-        <v>-1534450.4890246154</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>2765517.75</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="1"/>
-        <v>-489088.48902461538</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>2788510.25</v>
-      </c>
-      <c r="C11">
-        <f t="shared" si="1"/>
-        <v>-466095.98902461538</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>2815612.25</v>
-      </c>
-      <c r="C12">
-        <f t="shared" si="1"/>
-        <v>-438993.98902461538</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>2519609.75</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="1"/>
-        <v>-734996.48902461538</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>2528737.25</v>
-      </c>
-      <c r="C14">
-        <f t="shared" si="1"/>
-        <v>-725868.98902461538</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>100</v>
-      </c>
-      <c r="E16">
-        <f>SUM(E7:E14)/8 * 100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>2446575.451923077</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54643188-1494-4C27-944B-D377E8FB9B1B}">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10809,24 +10160,288 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>5804.6254577636728</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>5804.6254577636728</v>
+      </c>
       <c r="D16">
-        <f>SUM(D2:D14)/13 * 100</f>
-        <v>53.846153846153847</v>
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>87.5</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
         <v>87.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <f>AVERAGE(B2:B14)</f>
-        <v>3572.077204777645</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D08145B-C46C-4C93-88A6-B52C646370D6}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <f>IF(B2&gt;0, 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:E14" si="0">IF(B3&gt;0, 1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>51120.8046875</v>
+      </c>
+      <c r="C7">
+        <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
+        <v>51120.8046875</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <f>IF(C7&gt;0, 1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>61108.37109375</v>
+      </c>
+      <c r="C8">
+        <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
+        <v>61108.37109375</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>56102.08984375</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>56102.08984375</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>104585.375</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>104585.375</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>103256.1796875</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>103256.1796875</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>103122.8359375</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="1"/>
+        <v>103122.8359375</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>66476.8203125</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="1"/>
+        <v>66476.8203125</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>65967.171875</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="1"/>
+        <v>65967.171875</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>AVERAGE(B7:B14)</f>
+        <v>76467.4560546875</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C7:C14)</f>
+        <v>76467.4560546875</v>
+      </c>
+      <c r="D16">
+        <f>SUM(D7:D14)/8 * 100</f>
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <f>SUM(E7:E14)/8 * 100</f>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -10835,7 +10450,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D08145B-C46C-4C93-88A6-B52C646370D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3582B0E6-5A5B-4C02-98A3-54931C7DC318}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10918,19 +10533,19 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>51120.8046875</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <f>B7-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>51120.8046875</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <f>IF(C7&gt;0, 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -10938,19 +10553,19 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>61108.37109375</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C14" si="1">B8-(AVERAGE(B$2:B$6)+3*STDEV(B$2:B$6))</f>
-        <v>61108.37109375</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -10958,11 +10573,11 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>56102.08984375</v>
+        <v>2613.88256835938</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>56102.08984375</v>
+        <v>2613.88256835938</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -10978,11 +10593,11 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>104585.375</v>
+        <v>6067.1884765625</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>104585.375</v>
+        <v>6067.1884765625</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -10998,11 +10613,11 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>103256.1796875</v>
+        <v>6112.1142578125</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>103256.1796875</v>
+        <v>6112.1142578125</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
@@ -11018,11 +10633,11 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>103122.8359375</v>
+        <v>5914.23291015625</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>103122.8359375</v>
+        <v>5914.23291015625</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
@@ -11038,19 +10653,19 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>66476.8203125</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
-        <v>66476.8203125</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -11058,35 +10673,35 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>65967.171875</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
-        <v>65967.171875</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D16">
         <f>SUM(D2:D14)/13 * 100</f>
-        <v>61.53846153846154</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="E16">
         <f>SUM(E7:E14)/8 * 100</f>
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17">
         <f>AVERAGE(B2:B14)</f>
-        <v>47056.896033653844</v>
+        <v>1592.8783240685102</v>
       </c>
     </row>
   </sheetData>

--- a/PIMMS Validation work/Skyline comparison data/Skyline_all_analyte_detection_frequency.xlsx
+++ b/PIMMS Validation work/Skyline comparison data/Skyline_all_analyte_detection_frequency.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\PFAS-IMplementor-for-Mass-Spectrometry--PIMMS-\PIMMS Validation work\Skyline comparison data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFE25CF-3AD2-400E-9127-5852F575A333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9773AE2-CC8B-4492-88FB-38E52924AF1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="32" activeTab="36" xr2:uid="{79560FBE-CED3-4771-A659-93F59127F910}"/>
   </bookViews>
@@ -8874,6 +8874,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21609D0F-1D77-4F49-A66E-58A7EFF8AA53}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
@@ -9662,6 +9667,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4310F7-F432-4C06-AE6D-4EA24129CE24}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
